--- a/docs/主武器射速榜.xlsx
+++ b/docs/主武器射速榜.xlsx
@@ -43,6 +43,11 @@
       <sz val="9"/>
     </font>
     <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00202327"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
@@ -81,7 +86,7 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="001F1F1F"/>
+      <color rgb="00202327"/>
       <sz val="10"/>
     </font>
     <font>
@@ -114,11 +119,6 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="001F1F1F"/>
-      <sz val="9"/>
-    </font>
   </fonts>
   <fills count="18">
     <fill>
@@ -135,6 +135,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4F5F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -160,11 +165,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="007F8C8D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -324,94 +324,100 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -521,11 +527,11 @@
   <oneCellAnchor>
     <from>
       <col>2</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -545,87 +551,87 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>3</col>
+      <colOff>133350</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>2</col>
-      <colOff>247650</colOff>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>476250</colOff>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>704850</colOff>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>19050</colOff>
-      <row>5</row>
-      <rowOff>200025</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -670,12 +676,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
-      <colOff>19050</colOff>
+      <col>9</col>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -695,12 +701,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
-      <colOff>247650</colOff>
+      <col>11</col>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -745,12 +751,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>19050</colOff>
+      <col>15</col>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -770,12 +776,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>247650</colOff>
+      <col>17</col>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -821,11 +827,11 @@
   <oneCellAnchor>
     <from>
       <col>20</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -845,12 +851,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>247650</colOff>
+      <col>21</col>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -895,12 +901,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>26</col>
-      <colOff>19050</colOff>
+      <col>28</col>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="17" name="Image 17" descr="Picture"/>
@@ -920,12 +926,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>26</col>
-      <colOff>247650</colOff>
+      <col>27</col>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="18" name="Image 18" descr="Picture"/>
@@ -970,12 +976,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>19050</colOff>
+      <col>3</col>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="20" name="Image 20" descr="Picture"/>
@@ -995,12 +1001,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>247650</colOff>
+      <col>3</col>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="21" name="Image 21" descr="Picture"/>
@@ -1045,62 +1051,62 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>9</col>
+      <colOff>133350</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>8</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="23" name="Image 23" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>247650</colOff>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>476250</colOff>
-      <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -1146,11 +1152,11 @@
   <oneCellAnchor>
     <from>
       <col>14</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="27" name="Image 27" descr="Picture"/>
@@ -1170,12 +1176,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>247650</colOff>
+      <col>16</col>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="28" name="Image 28" descr="Picture"/>
@@ -1195,12 +1201,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>476250</colOff>
+      <col>17</col>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="29" name="Image 29" descr="Picture"/>
@@ -1246,11 +1252,11 @@
   <oneCellAnchor>
     <from>
       <col>20</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="31" name="Image 31" descr="Picture"/>
@@ -1271,11 +1277,11 @@
   <oneCellAnchor>
     <from>
       <col>20</col>
-      <colOff>247650</colOff>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="32" name="Image 32" descr="Picture"/>
@@ -1295,12 +1301,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>476250</colOff>
+      <col>21</col>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="33" name="Image 33" descr="Picture"/>
@@ -1346,11 +1352,11 @@
   <oneCellAnchor>
     <from>
       <col>26</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="35" name="Image 35" descr="Picture"/>
@@ -1370,12 +1376,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>26</col>
-      <colOff>247650</colOff>
+      <col>27</col>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="36" name="Image 36" descr="Picture"/>
@@ -1395,12 +1401,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>26</col>
-      <colOff>476250</colOff>
+      <col>29</col>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="37" name="Image 37" descr="Picture"/>
@@ -1445,12 +1451,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>19050</colOff>
+      <col>3</col>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="39" name="Image 39" descr="Picture"/>
@@ -1470,12 +1476,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>247650</colOff>
+      <col>3</col>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="40" name="Image 40" descr="Picture"/>
@@ -1520,12 +1526,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
-      <colOff>19050</colOff>
+      <col>9</col>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="42" name="Image 42" descr="Picture"/>
@@ -1545,12 +1551,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
-      <colOff>247650</colOff>
+      <col>10</col>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="43" name="Image 43" descr="Picture"/>
@@ -1596,11 +1602,11 @@
   <oneCellAnchor>
     <from>
       <col>14</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="45" name="Image 45" descr="Picture"/>
@@ -1620,12 +1626,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>247650</colOff>
+      <col>16</col>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="46" name="Image 46" descr="Picture"/>
@@ -1645,12 +1651,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>476250</colOff>
+      <col>16</col>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="47" name="Image 47" descr="Picture"/>
@@ -1696,11 +1702,11 @@
   <oneCellAnchor>
     <from>
       <col>20</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="49" name="Image 49" descr="Picture"/>
@@ -1720,12 +1726,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>247650</colOff>
+      <col>21</col>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="50" name="Image 50" descr="Picture"/>
@@ -1745,12 +1751,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>476250</colOff>
+      <col>22</col>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="51" name="Image 51" descr="Picture"/>
@@ -1795,62 +1801,62 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>28</col>
+      <colOff>133350</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>26</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="53" name="Image 53" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>26</col>
-      <colOff>247650</colOff>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>29</col>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="54" name="Image 54" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>26</col>
-      <colOff>476250</colOff>
-      <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="55" name="Image 55" descr="Picture"/>
@@ -1895,12 +1901,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>19050</colOff>
+      <col>4</col>
+      <colOff>133350</colOff>
       <row>17</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="57" name="Image 57" descr="Picture"/>
@@ -1920,12 +1926,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>247650</colOff>
+      <col>5</col>
+      <colOff>133350</colOff>
       <row>17</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="58" name="Image 58" descr="Picture"/>
@@ -1971,11 +1977,11 @@
   <oneCellAnchor>
     <from>
       <col>2</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="60" name="Image 60" descr="Picture"/>
@@ -1995,12 +2001,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>247650</colOff>
+      <col>4</col>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="61" name="Image 61" descr="Picture"/>
@@ -2020,12 +2026,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>476250</colOff>
+      <col>3</col>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="62" name="Image 62" descr="Picture"/>
@@ -2071,11 +2077,11 @@
   <oneCellAnchor>
     <from>
       <col>8</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="64" name="Image 64" descr="Picture"/>
@@ -2095,137 +2101,137 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>9</col>
+      <colOff>133350</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>133350</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>8</col>
-      <colOff>247650</colOff>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="65" name="Image 65" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>476250</colOff>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="66" name="Image 66" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>704850</colOff>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="67" name="Image 67" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>19050</colOff>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>200025</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="68" name="Image 68" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>247650</colOff>
-      <row>21</row>
-      <rowOff>200025</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="69" name="Image 69" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>476250</colOff>
-      <row>21</row>
-      <rowOff>200025</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="70" name="Image 70" descr="Picture"/>
@@ -2271,11 +2277,11 @@
   <oneCellAnchor>
     <from>
       <col>14</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="72" name="Image 72" descr="Picture"/>
@@ -2295,12 +2301,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>247650</colOff>
+      <col>15</col>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="73" name="Image 73" descr="Picture"/>
@@ -2320,12 +2326,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>476250</colOff>
+      <col>15</col>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="74" name="Image 74" descr="Picture"/>
@@ -2370,12 +2376,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>19050</colOff>
+      <col>21</col>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="76" name="Image 76" descr="Picture"/>
@@ -2395,12 +2401,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>247650</colOff>
+      <col>21</col>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="77" name="Image 77" descr="Picture"/>
@@ -2445,37 +2451,37 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>27</col>
+      <colOff>133350</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="79" name="Image 79" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>26</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="79" name="Image 79" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>26</col>
-      <colOff>247650</colOff>
-      <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="80" name="Image 80" descr="Picture"/>
@@ -2520,12 +2526,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>19050</colOff>
+      <col>4</col>
+      <colOff>133350</colOff>
       <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="82" name="Image 82" descr="Picture"/>
@@ -2545,12 +2551,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>247650</colOff>
+      <col>3</col>
+      <colOff>133350</colOff>
       <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="83" name="Image 83" descr="Picture"/>
@@ -2596,11 +2602,11 @@
   <oneCellAnchor>
     <from>
       <col>8</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="85" name="Image 85" descr="Picture"/>
@@ -2620,12 +2626,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
-      <colOff>247650</colOff>
+      <col>9</col>
+      <colOff>133350</colOff>
       <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="86" name="Image 86" descr="Picture"/>
@@ -2671,11 +2677,11 @@
   <oneCellAnchor>
     <from>
       <col>14</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="88" name="Image 88" descr="Picture"/>
@@ -2695,12 +2701,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>247650</colOff>
+      <col>15</col>
+      <colOff>133350</colOff>
       <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="89" name="Image 89" descr="Picture"/>
@@ -2720,12 +2726,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>476250</colOff>
+      <col>15</col>
+      <colOff>133350</colOff>
       <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="90" name="Image 90" descr="Picture"/>
@@ -2771,11 +2777,11 @@
   <oneCellAnchor>
     <from>
       <col>20</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="92" name="Image 92" descr="Picture"/>
@@ -2795,12 +2801,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>247650</colOff>
+      <col>21</col>
+      <colOff>133350</colOff>
       <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="93" name="Image 93" descr="Picture"/>
@@ -2820,12 +2826,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>476250</colOff>
+      <col>23</col>
+      <colOff>133350</colOff>
       <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="94" name="Image 94" descr="Picture"/>
@@ -2870,12 +2876,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>19050</colOff>
+      <col>4</col>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="96" name="Image 96" descr="Picture"/>
@@ -2895,12 +2901,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>247650</colOff>
+      <col>3</col>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="97" name="Image 97" descr="Picture"/>
@@ -2920,12 +2926,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>476250</colOff>
+      <col>4</col>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="98" name="Image 98" descr="Picture"/>
@@ -2971,11 +2977,11 @@
   <oneCellAnchor>
     <from>
       <col>8</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="100" name="Image 100" descr="Picture"/>
@@ -2995,12 +3001,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
-      <colOff>247650</colOff>
+      <col>9</col>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="101" name="Image 101" descr="Picture"/>
@@ -3020,12 +3026,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
-      <colOff>476250</colOff>
+      <col>11</col>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="102" name="Image 102" descr="Picture"/>
@@ -3070,12 +3076,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>19050</colOff>
+      <col>16</col>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="104" name="Image 104" descr="Picture"/>
@@ -3095,12 +3101,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>247650</colOff>
+      <col>15</col>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="105" name="Image 105" descr="Picture"/>
@@ -3120,12 +3126,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>476250</colOff>
+      <col>16</col>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="106" name="Image 106" descr="Picture"/>
@@ -3170,12 +3176,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>19050</colOff>
+      <col>22</col>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="108" name="Image 108" descr="Picture"/>
@@ -3195,12 +3201,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>247650</colOff>
+      <col>23</col>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="109" name="Image 109" descr="Picture"/>
@@ -3245,12 +3251,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>26</col>
-      <colOff>19050</colOff>
+      <col>27</col>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="111" name="Image 111" descr="Picture"/>
@@ -3270,12 +3276,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>26</col>
-      <colOff>247650</colOff>
+      <col>29</col>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="112" name="Image 112" descr="Picture"/>
@@ -3320,12 +3326,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>19050</colOff>
+      <col>4</col>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="114" name="Image 114" descr="Picture"/>
@@ -3345,12 +3351,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>247650</colOff>
+      <col>5</col>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="115" name="Image 115" descr="Picture"/>
@@ -3396,11 +3402,11 @@
   <oneCellAnchor>
     <from>
       <col>8</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="117" name="Image 117" descr="Picture"/>
@@ -3420,12 +3426,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
-      <colOff>247650</colOff>
+      <col>10</col>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="118" name="Image 118" descr="Picture"/>
@@ -3471,11 +3477,11 @@
   <oneCellAnchor>
     <from>
       <col>14</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="120" name="Image 120" descr="Picture"/>
@@ -3495,12 +3501,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>247650</colOff>
+      <col>17</col>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="121" name="Image 121" descr="Picture"/>
@@ -3545,12 +3551,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>19050</colOff>
+      <col>22</col>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="123" name="Image 123" descr="Picture"/>
@@ -3570,12 +3576,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>247650</colOff>
+      <col>22</col>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="124" name="Image 124" descr="Picture"/>
@@ -3595,12 +3601,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>476250</colOff>
+      <col>23</col>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="125" name="Image 125" descr="Picture"/>
@@ -3645,12 +3651,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>26</col>
-      <colOff>19050</colOff>
+      <col>27</col>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="127" name="Image 127" descr="Picture"/>
@@ -3670,12 +3676,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>26</col>
-      <colOff>247650</colOff>
+      <col>29</col>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="128" name="Image 128" descr="Picture"/>
@@ -3721,11 +3727,11 @@
   <oneCellAnchor>
     <from>
       <col>2</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>37</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="130" name="Image 130" descr="Picture"/>
@@ -3745,12 +3751,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>247650</colOff>
+      <col>3</col>
+      <colOff>133350</colOff>
       <row>37</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="131" name="Image 131" descr="Picture"/>
@@ -3796,11 +3802,11 @@
   <oneCellAnchor>
     <from>
       <col>8</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>37</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="133" name="Image 133" descr="Picture"/>
@@ -3820,12 +3826,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
-      <colOff>247650</colOff>
+      <col>9</col>
+      <colOff>133350</colOff>
       <row>37</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="134" name="Image 134" descr="Picture"/>
@@ -3845,12 +3851,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
-      <colOff>476250</colOff>
+      <col>11</col>
+      <colOff>133350</colOff>
       <row>37</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="135" name="Image 135" descr="Picture"/>
@@ -3896,11 +3902,11 @@
   <oneCellAnchor>
     <from>
       <col>14</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>37</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="137" name="Image 137" descr="Picture"/>
@@ -3920,12 +3926,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>247650</colOff>
+      <col>17</col>
+      <colOff>133350</colOff>
       <row>37</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="138" name="Image 138" descr="Picture"/>
@@ -3971,11 +3977,11 @@
   <oneCellAnchor>
     <from>
       <col>20</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>37</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="140" name="Image 140" descr="Picture"/>
@@ -3995,12 +4001,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>247650</colOff>
+      <col>21</col>
+      <colOff>133350</colOff>
       <row>37</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="141" name="Image 141" descr="Picture"/>
@@ -4020,12 +4026,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>476250</colOff>
+      <col>22</col>
+      <colOff>133350</colOff>
       <row>37</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="142" name="Image 142" descr="Picture"/>
@@ -4076,11 +4082,11 @@
   <oneCellAnchor>
     <from>
       <col>2</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -4100,12 +4106,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>247650</colOff>
+      <col>5</col>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -4151,11 +4157,11 @@
   <oneCellAnchor>
     <from>
       <col>8</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -4175,12 +4181,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
-      <colOff>247650</colOff>
+      <col>9</col>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -4226,11 +4232,11 @@
   <oneCellAnchor>
     <from>
       <col>14</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -4251,11 +4257,11 @@
   <oneCellAnchor>
     <from>
       <col>14</col>
-      <colOff>247650</colOff>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -4300,12 +4306,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>19050</colOff>
+      <col>22</col>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -4325,12 +4331,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>247650</colOff>
+      <col>21</col>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -4350,12 +4356,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>476250</colOff>
+      <col>23</col>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -4400,12 +4406,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>26</col>
-      <colOff>19050</colOff>
+      <col>28</col>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -4425,12 +4431,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>26</col>
-      <colOff>247650</colOff>
+      <col>29</col>
+      <colOff>133350</colOff>
       <row>5</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
@@ -4475,62 +4481,62 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>3</col>
+      <colOff>133350</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>133350</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>2</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>247650</colOff>
-      <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>476250</colOff>
-      <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="20" name="Image 20" descr="Picture"/>
@@ -4575,12 +4581,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
-      <colOff>19050</colOff>
+      <col>9</col>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="22" name="Image 22" descr="Picture"/>
@@ -4600,12 +4606,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
-      <colOff>247650</colOff>
+      <col>10</col>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="23" name="Image 23" descr="Picture"/>
@@ -4651,11 +4657,11 @@
   <oneCellAnchor>
     <from>
       <col>14</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -4675,37 +4681,37 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>16</col>
+      <colOff>133350</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>14</col>
-      <colOff>247650</colOff>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>14</col>
-      <colOff>476250</colOff>
-      <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="27" name="Image 27" descr="Picture"/>
@@ -4750,12 +4756,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>19050</colOff>
+      <col>21</col>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="29" name="Image 29" descr="Picture"/>
@@ -4775,12 +4781,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>247650</colOff>
+      <col>22</col>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="30" name="Image 30" descr="Picture"/>
@@ -4825,12 +4831,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>26</col>
-      <colOff>19050</colOff>
+      <col>27</col>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="32" name="Image 32" descr="Picture"/>
@@ -4850,12 +4856,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>26</col>
-      <colOff>247650</colOff>
+      <col>28</col>
+      <colOff>133350</colOff>
       <row>9</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="33" name="Image 33" descr="Picture"/>
@@ -4901,11 +4907,11 @@
   <oneCellAnchor>
     <from>
       <col>2</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="35" name="Image 35" descr="Picture"/>
@@ -4925,12 +4931,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>247650</colOff>
+      <col>5</col>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="36" name="Image 36" descr="Picture"/>
@@ -4975,62 +4981,62 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>10</col>
+      <colOff>133350</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>8</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="38" name="Image 38" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>247650</colOff>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="39" name="Image 39" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>476250</colOff>
-      <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="40" name="Image 40" descr="Picture"/>
@@ -5075,12 +5081,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>19050</colOff>
+      <col>16</col>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="42" name="Image 42" descr="Picture"/>
@@ -5100,12 +5106,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>247650</colOff>
+      <col>17</col>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="43" name="Image 43" descr="Picture"/>
@@ -5151,11 +5157,11 @@
   <oneCellAnchor>
     <from>
       <col>20</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="45" name="Image 45" descr="Picture"/>
@@ -5175,12 +5181,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>247650</colOff>
+      <col>21</col>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="46" name="Image 46" descr="Picture"/>
@@ -5226,11 +5232,11 @@
   <oneCellAnchor>
     <from>
       <col>26</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="48" name="Image 48" descr="Picture"/>
@@ -5250,12 +5256,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>26</col>
-      <colOff>247650</colOff>
+      <col>28</col>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="49" name="Image 49" descr="Picture"/>
@@ -5275,12 +5281,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>26</col>
-      <colOff>476250</colOff>
+      <col>29</col>
+      <colOff>133350</colOff>
       <row>13</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="50" name="Image 50" descr="Picture"/>
@@ -5326,11 +5332,11 @@
   <oneCellAnchor>
     <from>
       <col>2</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>17</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="52" name="Image 52" descr="Picture"/>
@@ -5350,12 +5356,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>247650</colOff>
+      <col>5</col>
+      <colOff>133350</colOff>
       <row>17</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="53" name="Image 53" descr="Picture"/>
@@ -5401,11 +5407,11 @@
   <oneCellAnchor>
     <from>
       <col>8</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>17</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="55" name="Image 55" descr="Picture"/>
@@ -5425,12 +5431,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
-      <colOff>247650</colOff>
+      <col>9</col>
+      <colOff>133350</colOff>
       <row>17</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="56" name="Image 56" descr="Picture"/>
@@ -5476,11 +5482,11 @@
   <oneCellAnchor>
     <from>
       <col>14</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>17</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="58" name="Image 58" descr="Picture"/>
@@ -5500,12 +5506,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>247650</colOff>
+      <col>15</col>
+      <colOff>133350</colOff>
       <row>17</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="59" name="Image 59" descr="Picture"/>
@@ -5525,12 +5531,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>476250</colOff>
+      <col>16</col>
+      <colOff>133350</colOff>
       <row>17</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="60" name="Image 60" descr="Picture"/>
@@ -5576,11 +5582,11 @@
   <oneCellAnchor>
     <from>
       <col>20</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>17</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="62" name="Image 62" descr="Picture"/>
@@ -5600,12 +5606,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>247650</colOff>
+      <col>21</col>
+      <colOff>133350</colOff>
       <row>17</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="63" name="Image 63" descr="Picture"/>
@@ -5625,12 +5631,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>476250</colOff>
+      <col>23</col>
+      <colOff>133350</colOff>
       <row>17</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="64" name="Image 64" descr="Picture"/>
@@ -5675,62 +5681,62 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>27</col>
+      <colOff>133350</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>26</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>17</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="66" name="Image 66" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>26</col>
-      <colOff>247650</colOff>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>29</col>
+      <colOff>133350</colOff>
       <row>17</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="67" name="Image 67" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>26</col>
-      <colOff>476250</colOff>
-      <row>17</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="68" name="Image 68" descr="Picture"/>
@@ -5776,11 +5782,11 @@
   <oneCellAnchor>
     <from>
       <col>2</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="70" name="Image 70" descr="Picture"/>
@@ -5800,12 +5806,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>247650</colOff>
+      <col>4</col>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="71" name="Image 71" descr="Picture"/>
@@ -5851,11 +5857,11 @@
   <oneCellAnchor>
     <from>
       <col>8</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="73" name="Image 73" descr="Picture"/>
@@ -5875,137 +5881,137 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>9</col>
+      <colOff>133350</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="74" name="Image 74" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>133350</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="75" name="Image 75" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>8</col>
-      <colOff>247650</colOff>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="74" name="Image 74" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>476250</colOff>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="76" name="Image 76" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="75" name="Image 75" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>704850</colOff>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="77" name="Image 77" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="76" name="Image 76" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>19050</colOff>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="78" name="Image 78" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>200025</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="77" name="Image 77" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>247650</colOff>
-      <row>21</row>
-      <rowOff>200025</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="78" name="Image 78" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>476250</colOff>
-      <row>21</row>
-      <rowOff>200025</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="79" name="Image 79" descr="Picture"/>
@@ -6050,12 +6056,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>19050</colOff>
+      <col>15</col>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="81" name="Image 81" descr="Picture"/>
@@ -6075,12 +6081,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>247650</colOff>
+      <col>16</col>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="82" name="Image 82" descr="Picture"/>
@@ -6125,12 +6131,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>19050</colOff>
+      <col>22</col>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="84" name="Image 84" descr="Picture"/>
@@ -6150,12 +6156,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>247650</colOff>
+      <col>21</col>
+      <colOff>133350</colOff>
       <row>21</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="85" name="Image 85" descr="Picture"/>
@@ -6200,37 +6206,37 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>3</col>
+      <colOff>133350</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="87" name="Image 87" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId87"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>2</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="87" name="Image 87" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId87"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>247650</colOff>
-      <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="88" name="Image 88" descr="Picture"/>
@@ -6275,37 +6281,37 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>10</col>
+      <colOff>133350</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="90" name="Image 90" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId90"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>8</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="90" name="Image 90" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId90"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>247650</colOff>
-      <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="91" name="Image 91" descr="Picture"/>
@@ -6351,11 +6357,11 @@
   <oneCellAnchor>
     <from>
       <col>14</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="93" name="Image 93" descr="Picture"/>
@@ -6376,11 +6382,11 @@
   <oneCellAnchor>
     <from>
       <col>14</col>
-      <colOff>247650</colOff>
+      <colOff>133350</colOff>
       <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="94" name="Image 94" descr="Picture"/>
@@ -6400,12 +6406,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>476250</colOff>
+      <col>16</col>
+      <colOff>133350</colOff>
       <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="95" name="Image 95" descr="Picture"/>
@@ -6450,12 +6456,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>19050</colOff>
+      <col>22</col>
+      <colOff>133350</colOff>
       <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="97" name="Image 97" descr="Picture"/>
@@ -6475,12 +6481,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>247650</colOff>
+      <col>21</col>
+      <colOff>133350</colOff>
       <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="98" name="Image 98" descr="Picture"/>
@@ -6525,62 +6531,62 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>27</col>
+      <colOff>133350</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="100" name="Image 100" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId100"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>26</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="100" name="Image 100" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId100"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>26</col>
-      <colOff>247650</colOff>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="101" name="Image 101" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId101"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>29</col>
+      <colOff>133350</colOff>
       <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="101" name="Image 101" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId101"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>26</col>
-      <colOff>476250</colOff>
-      <row>25</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="102" name="Image 102" descr="Picture"/>
@@ -6625,12 +6631,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>19050</colOff>
+      <col>4</col>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="104" name="Image 104" descr="Picture"/>
@@ -6650,12 +6656,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>247650</colOff>
+      <col>5</col>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="105" name="Image 105" descr="Picture"/>
@@ -6700,12 +6706,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
-      <colOff>19050</colOff>
+      <col>9</col>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="107" name="Image 107" descr="Picture"/>
@@ -6725,12 +6731,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
-      <colOff>247650</colOff>
+      <col>10</col>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="108" name="Image 108" descr="Picture"/>
@@ -6776,11 +6782,11 @@
   <oneCellAnchor>
     <from>
       <col>14</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="110" name="Image 110" descr="Picture"/>
@@ -6800,12 +6806,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>247650</colOff>
+      <col>15</col>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="111" name="Image 111" descr="Picture"/>
@@ -6850,62 +6856,62 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>21</col>
+      <colOff>133350</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="113" name="Image 113" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId113"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>20</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="113" name="Image 113" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId113"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>20</col>
-      <colOff>247650</colOff>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="114" name="Image 114" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId114"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>21</col>
+      <colOff>133350</colOff>
       <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="114" name="Image 114" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId114"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>20</col>
-      <colOff>476250</colOff>
-      <row>29</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="115" name="Image 115" descr="Picture"/>
@@ -6950,37 +6956,37 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>4</col>
+      <colOff>133350</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="117" name="Image 117" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId117"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>2</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="117" name="Image 117" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId117"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>247650</colOff>
-      <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="118" name="Image 118" descr="Picture"/>
@@ -7025,12 +7031,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
-      <colOff>19050</colOff>
+      <col>9</col>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="120" name="Image 120" descr="Picture"/>
@@ -7050,12 +7056,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
-      <colOff>247650</colOff>
+      <col>11</col>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="121" name="Image 121" descr="Picture"/>
@@ -7101,11 +7107,11 @@
   <oneCellAnchor>
     <from>
       <col>14</col>
-      <colOff>19050</colOff>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="123" name="Image 123" descr="Picture"/>
@@ -7125,12 +7131,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>247650</colOff>
+      <col>15</col>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="124" name="Image 124" descr="Picture"/>
@@ -7150,12 +7156,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>14</col>
-      <colOff>476250</colOff>
+      <col>16</col>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="125" name="Image 125" descr="Picture"/>
@@ -7200,12 +7206,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>19050</colOff>
+      <col>21</col>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="127" name="Image 127" descr="Picture"/>
@@ -7225,12 +7231,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
-      <colOff>247650</colOff>
+      <col>21</col>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="128" name="Image 128" descr="Picture"/>
@@ -7275,12 +7281,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>26</col>
-      <colOff>19050</colOff>
+      <col>28</col>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="130" name="Image 130" descr="Picture"/>
@@ -7300,12 +7306,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>26</col>
-      <colOff>247650</colOff>
+      <col>28</col>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="131" name="Image 131" descr="Picture"/>
@@ -7325,12 +7331,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>26</col>
-      <colOff>476250</colOff>
+      <col>29</col>
+      <colOff>133350</colOff>
       <row>33</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="228600" cy="190500"/>
+      <rowOff>209550</rowOff>
+    </from>
+    <ext cx="228600" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="132" name="Image 132" descr="Picture"/>
@@ -7778,65 +7784,65 @@
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="B4" s="11" t="n"/>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="D4" s="5" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="F4" s="5" t="n"/>
       <c r="H4" s="11" t="n"/>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="J4" s="5" t="n"/>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="L4" s="5" t="n"/>
       <c r="N4" s="11" t="n"/>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O4" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="P4" s="5" t="n"/>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="Q4" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="R4" s="5" t="n"/>
       <c r="T4" s="11" t="n"/>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="U4" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="V4" s="5" t="n"/>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="W4" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="X4" s="5" t="n"/>
       <c r="Z4" s="11" t="n"/>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AA4" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="AB4" s="5" t="n"/>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AC4" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
@@ -7844,101 +7850,101 @@
       <c r="AD4" s="5" t="n"/>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="B5" s="12" t="n"/>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>主 980</t>
         </is>
       </c>
       <c r="F5" s="5" t="n"/>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="H5" s="14" t="n"/>
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="J5" s="5" t="n"/>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="K5" s="13" t="inlineStr">
         <is>
           <t>主 980</t>
         </is>
       </c>
       <c r="L5" s="5" t="n"/>
-      <c r="N5" s="12" t="n"/>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="N5" s="14" t="n"/>
+      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="Q5" s="13" t="inlineStr">
         <is>
           <t>主 860/720</t>
         </is>
       </c>
       <c r="R5" s="5" t="n"/>
-      <c r="T5" s="12" t="n"/>
-      <c r="U5" s="4" t="inlineStr">
+      <c r="T5" s="14" t="n"/>
+      <c r="U5" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="V5" s="5" t="n"/>
-      <c r="W5" s="4" t="inlineStr">
+      <c r="W5" s="13" t="inlineStr">
         <is>
           <t>主 860/780</t>
         </is>
       </c>
       <c r="X5" s="5" t="n"/>
-      <c r="Z5" s="12" t="n"/>
-      <c r="AA5" s="4" t="inlineStr">
+      <c r="Z5" s="14" t="n"/>
+      <c r="AA5" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="AB5" s="5" t="n"/>
-      <c r="AC5" s="4" t="inlineStr">
+      <c r="AC5" s="13" t="inlineStr">
         <is>
           <t>主 900/800</t>
         </is>
       </c>
       <c r="AD5" s="5" t="n"/>
     </row>
-    <row r="6" ht="40" customHeight="1">
+    <row r="6" ht="34" customHeight="1">
       <c r="B6" s="3" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
       <c r="F6" s="5" t="n"/>
       <c r="H6" s="3" t="n"/>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="13" t="n"/>
-      <c r="K6" s="13" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
+      <c r="K6" s="15" t="n"/>
       <c r="L6" s="5" t="n"/>
       <c r="N6" s="3" t="n"/>
-      <c r="O6" s="13" t="n"/>
-      <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="13" t="n"/>
+      <c r="O6" s="15" t="n"/>
+      <c r="P6" s="15" t="n"/>
+      <c r="Q6" s="15" t="n"/>
       <c r="R6" s="5" t="n"/>
       <c r="T6" s="3" t="n"/>
-      <c r="U6" s="13" t="n"/>
-      <c r="V6" s="13" t="n"/>
-      <c r="W6" s="13" t="n"/>
+      <c r="U6" s="15" t="n"/>
+      <c r="V6" s="15" t="n"/>
+      <c r="W6" s="15" t="n"/>
       <c r="X6" s="5" t="n"/>
       <c r="Z6" s="3" t="n"/>
-      <c r="AA6" s="13" t="n"/>
-      <c r="AB6" s="13" t="n"/>
-      <c r="AC6" s="13" t="n"/>
+      <c r="AA6" s="15" t="n"/>
+      <c r="AB6" s="15" t="n"/>
+      <c r="AC6" s="15" t="n"/>
       <c r="AD6" s="5" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
@@ -8031,65 +8037,65 @@
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="B8" s="11" t="n"/>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="D8" s="5" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="F8" s="5" t="n"/>
       <c r="H8" s="11" t="n"/>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="J8" s="5" t="n"/>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="K8" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="L8" s="5" t="n"/>
       <c r="N8" s="11" t="n"/>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="O8" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="Q8" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="R8" s="5" t="n"/>
       <c r="T8" s="11" t="n"/>
-      <c r="U8" s="4" t="inlineStr">
+      <c r="U8" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="V8" s="5" t="n"/>
-      <c r="W8" s="4" t="inlineStr">
+      <c r="W8" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="X8" s="5" t="n"/>
       <c r="Z8" s="11" t="n"/>
-      <c r="AA8" s="4" t="inlineStr">
+      <c r="AA8" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="AB8" s="5" t="n"/>
-      <c r="AC8" s="4" t="inlineStr">
+      <c r="AC8" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
@@ -8097,97 +8103,97 @@
       <c r="AD8" s="5" t="n"/>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>主 850</t>
         </is>
       </c>
       <c r="F9" s="5" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="H9" s="14" t="n"/>
+      <c r="I9" s="13" t="inlineStr">
         <is>
           <t>副 1100</t>
         </is>
       </c>
       <c r="J9" s="5" t="n"/>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>主 850</t>
         </is>
       </c>
       <c r="L9" s="5" t="n"/>
-      <c r="N9" s="12" t="n"/>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="N9" s="14" t="n"/>
+      <c r="O9" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="Q9" s="13" t="inlineStr">
         <is>
           <t>主 780/650</t>
         </is>
       </c>
       <c r="R9" s="5" t="n"/>
-      <c r="T9" s="12" t="n"/>
-      <c r="U9" s="4" t="inlineStr">
+      <c r="T9" s="14" t="n"/>
+      <c r="U9" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="V9" s="5" t="n"/>
-      <c r="W9" s="4" t="inlineStr">
+      <c r="W9" s="13" t="inlineStr">
         <is>
           <t>主 850/720/690</t>
         </is>
       </c>
       <c r="X9" s="5" t="n"/>
-      <c r="Z9" s="12" t="n"/>
-      <c r="AA9" s="4" t="inlineStr">
+      <c r="Z9" s="14" t="n"/>
+      <c r="AA9" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="AB9" s="5" t="n"/>
-      <c r="AC9" s="4" t="inlineStr">
+      <c r="AC9" s="13" t="inlineStr">
         <is>
           <t>主 800/800</t>
         </is>
       </c>
       <c r="AD9" s="5" t="n"/>
     </row>
-    <row r="10" ht="20" customHeight="1">
+    <row r="10" ht="34" customHeight="1">
       <c r="B10" s="3" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="H10" s="3" t="n"/>
-      <c r="I10" s="13" t="n"/>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="13" t="n"/>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="15" t="n"/>
+      <c r="K10" s="15" t="n"/>
       <c r="L10" s="5" t="n"/>
       <c r="N10" s="3" t="n"/>
-      <c r="O10" s="13" t="n"/>
-      <c r="P10" s="13" t="n"/>
-      <c r="Q10" s="13" t="n"/>
+      <c r="O10" s="15" t="n"/>
+      <c r="P10" s="15" t="n"/>
+      <c r="Q10" s="15" t="n"/>
       <c r="R10" s="5" t="n"/>
       <c r="T10" s="3" t="n"/>
-      <c r="U10" s="13" t="n"/>
-      <c r="V10" s="13" t="n"/>
-      <c r="W10" s="13" t="n"/>
+      <c r="U10" s="15" t="n"/>
+      <c r="V10" s="15" t="n"/>
+      <c r="W10" s="15" t="n"/>
       <c r="X10" s="5" t="n"/>
       <c r="Z10" s="3" t="n"/>
-      <c r="AA10" s="13" t="n"/>
-      <c r="AB10" s="13" t="n"/>
-      <c r="AC10" s="13" t="n"/>
+      <c r="AA10" s="15" t="n"/>
+      <c r="AB10" s="15" t="n"/>
+      <c r="AC10" s="15" t="n"/>
       <c r="AD10" s="5" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -8279,65 +8285,65 @@
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="B12" s="11" t="n"/>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="D12" s="5" t="n"/>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="F12" s="5" t="n"/>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="J12" s="5" t="n"/>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K12" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="L12" s="5" t="n"/>
       <c r="N12" s="11" t="n"/>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="O12" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="4" t="inlineStr">
+      <c r="Q12" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="R12" s="5" t="n"/>
       <c r="T12" s="11" t="n"/>
-      <c r="U12" s="4" t="inlineStr">
+      <c r="U12" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="V12" s="5" t="n"/>
-      <c r="W12" s="4" t="inlineStr">
+      <c r="W12" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="X12" s="5" t="n"/>
       <c r="Z12" s="11" t="n"/>
-      <c r="AA12" s="4" t="inlineStr">
+      <c r="AA12" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="AB12" s="5" t="n"/>
-      <c r="AC12" s="4" t="inlineStr">
+      <c r="AC12" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
@@ -8345,97 +8351,97 @@
       <c r="AD12" s="5" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="D13" s="5" t="n"/>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>主 837</t>
         </is>
       </c>
       <c r="F13" s="5" t="n"/>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="H13" s="14" t="n"/>
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>副 1270</t>
         </is>
       </c>
       <c r="J13" s="5" t="n"/>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K13" s="13" t="inlineStr">
         <is>
           <t>主 850</t>
         </is>
       </c>
       <c r="L13" s="5" t="n"/>
-      <c r="N13" s="12" t="n"/>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="N13" s="14" t="n"/>
+      <c r="O13" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="Q13" s="13" t="inlineStr">
         <is>
           <t>主 800</t>
         </is>
       </c>
       <c r="R13" s="5" t="n"/>
-      <c r="T13" s="12" t="n"/>
-      <c r="U13" s="4" t="inlineStr">
+      <c r="T13" s="14" t="n"/>
+      <c r="U13" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="V13" s="5" t="n"/>
-      <c r="W13" s="4" t="inlineStr">
+      <c r="W13" s="13" t="inlineStr">
         <is>
           <t>主 800/690</t>
         </is>
       </c>
       <c r="X13" s="5" t="n"/>
-      <c r="Z13" s="12" t="n"/>
-      <c r="AA13" s="4" t="inlineStr">
+      <c r="Z13" s="14" t="n"/>
+      <c r="AA13" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="AB13" s="5" t="n"/>
-      <c r="AC13" s="4" t="inlineStr">
+      <c r="AC13" s="13" t="inlineStr">
         <is>
           <t>主 850/680</t>
         </is>
       </c>
       <c r="AD13" s="5" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
+    <row r="14" ht="34" customHeight="1">
       <c r="B14" s="3" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="H14" s="3" t="n"/>
-      <c r="I14" s="13" t="n"/>
-      <c r="J14" s="13" t="n"/>
-      <c r="K14" s="13" t="n"/>
+      <c r="I14" s="15" t="n"/>
+      <c r="J14" s="15" t="n"/>
+      <c r="K14" s="15" t="n"/>
       <c r="L14" s="5" t="n"/>
       <c r="N14" s="3" t="n"/>
-      <c r="O14" s="13" t="n"/>
-      <c r="P14" s="13" t="n"/>
-      <c r="Q14" s="13" t="n"/>
+      <c r="O14" s="15" t="n"/>
+      <c r="P14" s="15" t="n"/>
+      <c r="Q14" s="15" t="n"/>
       <c r="R14" s="5" t="n"/>
       <c r="T14" s="3" t="n"/>
-      <c r="U14" s="13" t="n"/>
-      <c r="V14" s="13" t="n"/>
-      <c r="W14" s="13" t="n"/>
+      <c r="U14" s="15" t="n"/>
+      <c r="V14" s="15" t="n"/>
+      <c r="W14" s="15" t="n"/>
       <c r="X14" s="5" t="n"/>
       <c r="Z14" s="3" t="n"/>
-      <c r="AA14" s="13" t="n"/>
-      <c r="AB14" s="13" t="n"/>
-      <c r="AC14" s="13" t="n"/>
+      <c r="AA14" s="15" t="n"/>
+      <c r="AB14" s="15" t="n"/>
+      <c r="AC14" s="15" t="n"/>
       <c r="AD14" s="5" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -8446,7 +8452,7 @@
         </is>
       </c>
       <c r="D15" s="5" t="n"/>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -8479,13 +8485,13 @@
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="B16" s="11" t="n"/>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="D16" s="5" t="n"/>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
@@ -8513,69 +8519,69 @@
       <c r="AD16" s="5" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>主 780/700</t>
         </is>
       </c>
       <c r="F17" s="5" t="n"/>
-      <c r="H17" s="12" t="n"/>
+      <c r="H17" s="14" t="n"/>
       <c r="I17" s="3" t="n"/>
       <c r="J17" s="5" t="n"/>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="5" t="n"/>
-      <c r="N17" s="12" t="n"/>
+      <c r="N17" s="14" t="n"/>
       <c r="O17" s="3" t="n"/>
       <c r="P17" s="5" t="n"/>
       <c r="Q17" s="3" t="n"/>
       <c r="R17" s="5" t="n"/>
-      <c r="T17" s="12" t="n"/>
+      <c r="T17" s="14" t="n"/>
       <c r="U17" s="3" t="n"/>
       <c r="V17" s="5" t="n"/>
       <c r="W17" s="3" t="n"/>
       <c r="X17" s="5" t="n"/>
-      <c r="Z17" s="12" t="n"/>
+      <c r="Z17" s="14" t="n"/>
       <c r="AA17" s="3" t="n"/>
       <c r="AB17" s="5" t="n"/>
       <c r="AC17" s="3" t="n"/>
       <c r="AD17" s="5" t="n"/>
     </row>
-    <row r="18" ht="20" customHeight="1">
+    <row r="18" ht="34" customHeight="1">
       <c r="B18" s="3" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="H18" s="3" t="n"/>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="13" t="n"/>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="15" t="n"/>
+      <c r="K18" s="15" t="n"/>
       <c r="L18" s="5" t="n"/>
       <c r="N18" s="3" t="n"/>
-      <c r="O18" s="13" t="n"/>
-      <c r="P18" s="13" t="n"/>
-      <c r="Q18" s="13" t="n"/>
+      <c r="O18" s="15" t="n"/>
+      <c r="P18" s="15" t="n"/>
+      <c r="Q18" s="15" t="n"/>
       <c r="R18" s="5" t="n"/>
       <c r="T18" s="3" t="n"/>
-      <c r="U18" s="13" t="n"/>
-      <c r="V18" s="13" t="n"/>
-      <c r="W18" s="13" t="n"/>
+      <c r="U18" s="15" t="n"/>
+      <c r="V18" s="15" t="n"/>
+      <c r="W18" s="15" t="n"/>
       <c r="X18" s="5" t="n"/>
       <c r="Z18" s="3" t="n"/>
-      <c r="AA18" s="13" t="n"/>
-      <c r="AB18" s="13" t="n"/>
-      <c r="AC18" s="13" t="n"/>
+      <c r="AA18" s="15" t="n"/>
+      <c r="AB18" s="15" t="n"/>
+      <c r="AC18" s="15" t="n"/>
       <c r="AD18" s="5" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
@@ -8668,65 +8674,65 @@
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="B20" s="11" t="n"/>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="F20" s="5" t="n"/>
       <c r="H20" s="11" t="n"/>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I20" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="J20" s="5" t="n"/>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K20" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="N20" s="11" t="n"/>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="O20" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="4" t="inlineStr">
+      <c r="Q20" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="R20" s="5" t="n"/>
       <c r="T20" s="11" t="n"/>
-      <c r="U20" s="4" t="inlineStr">
+      <c r="U20" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="V20" s="5" t="n"/>
-      <c r="W20" s="4" t="inlineStr">
+      <c r="W20" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="X20" s="5" t="n"/>
       <c r="Z20" s="11" t="n"/>
-      <c r="AA20" s="4" t="inlineStr">
+      <c r="AA20" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="AB20" s="5" t="n"/>
-      <c r="AC20" s="4" t="inlineStr">
+      <c r="AC20" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
@@ -8734,97 +8740,97 @@
       <c r="AD20" s="5" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="D21" s="5" t="n"/>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>主 740/675</t>
         </is>
       </c>
       <c r="F21" s="5" t="n"/>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="J21" s="5" t="n"/>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K21" s="13" t="inlineStr">
         <is>
           <t>主 750/650</t>
         </is>
       </c>
       <c r="L21" s="5" t="n"/>
-      <c r="N21" s="12" t="n"/>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="N21" s="14" t="n"/>
+      <c r="O21" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="4" t="inlineStr">
+      <c r="Q21" s="13" t="inlineStr">
         <is>
           <t>主 700</t>
         </is>
       </c>
       <c r="R21" s="5" t="n"/>
-      <c r="T21" s="12" t="n"/>
-      <c r="U21" s="4" t="inlineStr">
+      <c r="T21" s="14" t="n"/>
+      <c r="U21" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="V21" s="5" t="n"/>
-      <c r="W21" s="4" t="inlineStr">
+      <c r="W21" s="13" t="inlineStr">
         <is>
           <t>主 749/650</t>
         </is>
       </c>
       <c r="X21" s="5" t="n"/>
-      <c r="Z21" s="12" t="n"/>
-      <c r="AA21" s="4" t="inlineStr">
+      <c r="Z21" s="14" t="n"/>
+      <c r="AA21" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="AB21" s="5" t="n"/>
-      <c r="AC21" s="4" t="inlineStr">
+      <c r="AC21" s="13" t="inlineStr">
         <is>
           <t>主 700/650</t>
         </is>
       </c>
       <c r="AD21" s="5" t="n"/>
     </row>
-    <row r="22" ht="40" customHeight="1">
+    <row r="22" ht="34" customHeight="1">
       <c r="B22" s="3" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="H22" s="3" t="n"/>
-      <c r="I22" s="13" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="13" t="n"/>
+      <c r="I22" s="15" t="n"/>
+      <c r="J22" s="15" t="n"/>
+      <c r="K22" s="15" t="n"/>
       <c r="L22" s="5" t="n"/>
       <c r="N22" s="3" t="n"/>
-      <c r="O22" s="13" t="n"/>
-      <c r="P22" s="13" t="n"/>
-      <c r="Q22" s="13" t="n"/>
+      <c r="O22" s="15" t="n"/>
+      <c r="P22" s="15" t="n"/>
+      <c r="Q22" s="15" t="n"/>
       <c r="R22" s="5" t="n"/>
       <c r="T22" s="3" t="n"/>
-      <c r="U22" s="13" t="n"/>
-      <c r="V22" s="13" t="n"/>
-      <c r="W22" s="13" t="n"/>
+      <c r="U22" s="15" t="n"/>
+      <c r="V22" s="15" t="n"/>
+      <c r="W22" s="15" t="n"/>
       <c r="X22" s="5" t="n"/>
       <c r="Z22" s="3" t="n"/>
-      <c r="AA22" s="13" t="n"/>
-      <c r="AB22" s="13" t="n"/>
-      <c r="AC22" s="13" t="n"/>
+      <c r="AA22" s="15" t="n"/>
+      <c r="AB22" s="15" t="n"/>
+      <c r="AC22" s="15" t="n"/>
       <c r="AD22" s="5" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -8904,52 +8910,52 @@
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="B24" s="11" t="n"/>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="D24" s="5" t="n"/>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="F24" s="5" t="n"/>
       <c r="H24" s="11" t="n"/>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="J24" s="5" t="n"/>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K24" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="L24" s="5" t="n"/>
       <c r="N24" s="11" t="n"/>
-      <c r="O24" s="4" t="inlineStr">
+      <c r="O24" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="4" t="inlineStr">
+      <c r="Q24" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="R24" s="5" t="n"/>
       <c r="T24" s="11" t="n"/>
-      <c r="U24" s="4" t="inlineStr">
+      <c r="U24" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="V24" s="5" t="n"/>
-      <c r="W24" s="4" t="inlineStr">
+      <c r="W24" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
@@ -8962,93 +8968,93 @@
       <c r="AD24" s="5" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="D25" s="5" t="n"/>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>主 730/720</t>
         </is>
       </c>
       <c r="F25" s="5" t="n"/>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="H25" s="14" t="n"/>
+      <c r="I25" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="J25" s="5" t="n"/>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="K25" s="13" t="inlineStr">
         <is>
           <t>主 749/670</t>
         </is>
       </c>
       <c r="L25" s="5" t="n"/>
-      <c r="N25" s="12" t="n"/>
-      <c r="O25" s="4" t="inlineStr">
+      <c r="N25" s="14" t="n"/>
+      <c r="O25" s="13" t="inlineStr">
         <is>
           <t>副 765</t>
         </is>
       </c>
       <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="4" t="inlineStr">
+      <c r="Q25" s="13" t="inlineStr">
         <is>
           <t>主 750</t>
         </is>
       </c>
       <c r="R25" s="5" t="n"/>
-      <c r="T25" s="12" t="n"/>
-      <c r="U25" s="4" t="inlineStr">
+      <c r="T25" s="14" t="n"/>
+      <c r="U25" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="V25" s="5" t="n"/>
-      <c r="W25" s="4" t="inlineStr">
+      <c r="W25" s="13" t="inlineStr">
         <is>
           <t>主 700/680</t>
         </is>
       </c>
       <c r="X25" s="5" t="n"/>
-      <c r="Z25" s="12" t="n"/>
+      <c r="Z25" s="14" t="n"/>
       <c r="AA25" s="3" t="n"/>
       <c r="AB25" s="5" t="n"/>
       <c r="AC25" s="3" t="n"/>
       <c r="AD25" s="5" t="n"/>
     </row>
-    <row r="26" ht="20" customHeight="1">
+    <row r="26" ht="34" customHeight="1">
       <c r="B26" s="3" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="H26" s="3" t="n"/>
-      <c r="I26" s="13" t="n"/>
-      <c r="J26" s="13" t="n"/>
-      <c r="K26" s="13" t="n"/>
+      <c r="I26" s="15" t="n"/>
+      <c r="J26" s="15" t="n"/>
+      <c r="K26" s="15" t="n"/>
       <c r="L26" s="5" t="n"/>
       <c r="N26" s="3" t="n"/>
-      <c r="O26" s="13" t="n"/>
-      <c r="P26" s="13" t="n"/>
-      <c r="Q26" s="13" t="n"/>
+      <c r="O26" s="15" t="n"/>
+      <c r="P26" s="15" t="n"/>
+      <c r="Q26" s="15" t="n"/>
       <c r="R26" s="5" t="n"/>
       <c r="T26" s="3" t="n"/>
-      <c r="U26" s="13" t="n"/>
-      <c r="V26" s="13" t="n"/>
-      <c r="W26" s="13" t="n"/>
+      <c r="U26" s="15" t="n"/>
+      <c r="V26" s="15" t="n"/>
+      <c r="W26" s="15" t="n"/>
       <c r="X26" s="5" t="n"/>
       <c r="Z26" s="3" t="n"/>
-      <c r="AA26" s="13" t="n"/>
-      <c r="AB26" s="13" t="n"/>
-      <c r="AC26" s="13" t="n"/>
+      <c r="AA26" s="15" t="n"/>
+      <c r="AB26" s="15" t="n"/>
+      <c r="AC26" s="15" t="n"/>
       <c r="AD26" s="5" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>Ⅳ</t>
         </is>
@@ -9141,65 +9147,65 @@
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="B28" s="11" t="n"/>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="D28" s="5" t="n"/>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="F28" s="5" t="n"/>
       <c r="H28" s="11" t="n"/>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="I28" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="J28" s="5" t="n"/>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="K28" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="N28" s="11" t="n"/>
-      <c r="O28" s="4" t="inlineStr">
+      <c r="O28" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="P28" s="5" t="n"/>
-      <c r="Q28" s="4" t="inlineStr">
+      <c r="Q28" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="R28" s="5" t="n"/>
       <c r="T28" s="11" t="n"/>
-      <c r="U28" s="4" t="inlineStr">
+      <c r="U28" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="V28" s="5" t="n"/>
-      <c r="W28" s="4" t="inlineStr">
+      <c r="W28" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="X28" s="5" t="n"/>
       <c r="Z28" s="11" t="n"/>
-      <c r="AA28" s="4" t="inlineStr">
+      <c r="AA28" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="AB28" s="5" t="n"/>
-      <c r="AC28" s="4" t="inlineStr">
+      <c r="AC28" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
@@ -9207,97 +9213,97 @@
       <c r="AD28" s="5" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="D29" s="5" t="n"/>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>主 690</t>
         </is>
       </c>
       <c r="F29" s="5" t="n"/>
-      <c r="H29" s="12" t="n"/>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="13" t="inlineStr">
         <is>
           <t>副 1100</t>
         </is>
       </c>
       <c r="J29" s="5" t="n"/>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="K29" s="12" t="inlineStr">
         <is>
           <t>主 -</t>
         </is>
       </c>
       <c r="L29" s="5" t="n"/>
-      <c r="N29" s="12" t="n"/>
-      <c r="O29" s="4" t="inlineStr">
+      <c r="N29" s="14" t="n"/>
+      <c r="O29" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="P29" s="5" t="n"/>
-      <c r="Q29" s="4" t="inlineStr">
+      <c r="Q29" s="13" t="inlineStr">
         <is>
           <t>主 650/650</t>
         </is>
       </c>
       <c r="R29" s="5" t="n"/>
-      <c r="T29" s="12" t="n"/>
-      <c r="U29" s="4" t="inlineStr">
+      <c r="T29" s="14" t="n"/>
+      <c r="U29" s="13" t="inlineStr">
         <is>
           <t>副 1270/1000</t>
         </is>
       </c>
       <c r="V29" s="5" t="n"/>
-      <c r="W29" s="4" t="inlineStr">
+      <c r="W29" s="13" t="inlineStr">
         <is>
           <t>主 675</t>
         </is>
       </c>
       <c r="X29" s="5" t="n"/>
-      <c r="Z29" s="12" t="n"/>
-      <c r="AA29" s="4" t="inlineStr">
+      <c r="Z29" s="14" t="n"/>
+      <c r="AA29" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="AB29" s="5" t="n"/>
-      <c r="AC29" s="4" t="inlineStr">
+      <c r="AC29" s="13" t="inlineStr">
         <is>
           <t>主 690</t>
         </is>
       </c>
       <c r="AD29" s="5" t="n"/>
     </row>
-    <row r="30" ht="20" customHeight="1">
+    <row r="30" ht="34" customHeight="1">
       <c r="B30" s="3" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
       <c r="F30" s="5" t="n"/>
       <c r="H30" s="3" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="13" t="n"/>
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="15" t="n"/>
+      <c r="K30" s="15" t="n"/>
       <c r="L30" s="5" t="n"/>
       <c r="N30" s="3" t="n"/>
-      <c r="O30" s="13" t="n"/>
-      <c r="P30" s="13" t="n"/>
-      <c r="Q30" s="13" t="n"/>
+      <c r="O30" s="15" t="n"/>
+      <c r="P30" s="15" t="n"/>
+      <c r="Q30" s="15" t="n"/>
       <c r="R30" s="5" t="n"/>
       <c r="T30" s="3" t="n"/>
-      <c r="U30" s="13" t="n"/>
-      <c r="V30" s="13" t="n"/>
-      <c r="W30" s="13" t="n"/>
+      <c r="U30" s="15" t="n"/>
+      <c r="V30" s="15" t="n"/>
+      <c r="W30" s="15" t="n"/>
       <c r="X30" s="5" t="n"/>
       <c r="Z30" s="3" t="n"/>
-      <c r="AA30" s="13" t="n"/>
-      <c r="AB30" s="13" t="n"/>
-      <c r="AC30" s="13" t="n"/>
+      <c r="AA30" s="15" t="n"/>
+      <c r="AB30" s="15" t="n"/>
+      <c r="AC30" s="15" t="n"/>
       <c r="AD30" s="5" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -9389,65 +9395,65 @@
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="B32" s="11" t="n"/>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="D32" s="5" t="n"/>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="F32" s="5" t="n"/>
       <c r="H32" s="11" t="n"/>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="I32" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="J32" s="5" t="n"/>
-      <c r="K32" s="4" t="inlineStr">
+      <c r="K32" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="L32" s="5" t="n"/>
       <c r="N32" s="11" t="n"/>
-      <c r="O32" s="4" t="inlineStr">
+      <c r="O32" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="P32" s="5" t="n"/>
-      <c r="Q32" s="4" t="inlineStr">
+      <c r="Q32" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="R32" s="5" t="n"/>
       <c r="T32" s="11" t="n"/>
-      <c r="U32" s="4" t="inlineStr">
+      <c r="U32" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="V32" s="5" t="n"/>
-      <c r="W32" s="4" t="inlineStr">
+      <c r="W32" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="X32" s="5" t="n"/>
       <c r="Z32" s="11" t="n"/>
-      <c r="AA32" s="4" t="inlineStr">
+      <c r="AA32" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="AB32" s="5" t="n"/>
-      <c r="AC32" s="4" t="inlineStr">
+      <c r="AC32" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
@@ -9455,97 +9461,97 @@
       <c r="AD32" s="5" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>副 765</t>
         </is>
       </c>
       <c r="D33" s="5" t="n"/>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>主 650</t>
         </is>
       </c>
       <c r="F33" s="5" t="n"/>
-      <c r="H33" s="12" t="n"/>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="H33" s="14" t="n"/>
+      <c r="I33" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="J33" s="5" t="n"/>
-      <c r="K33" s="4" t="inlineStr">
+      <c r="K33" s="13" t="inlineStr">
         <is>
           <t>主 650</t>
         </is>
       </c>
       <c r="L33" s="5" t="n"/>
-      <c r="N33" s="12" t="n"/>
-      <c r="O33" s="4" t="inlineStr">
+      <c r="N33" s="14" t="n"/>
+      <c r="O33" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="P33" s="5" t="n"/>
-      <c r="Q33" s="4" t="inlineStr">
+      <c r="Q33" s="12" t="inlineStr">
         <is>
           <t>主 -</t>
         </is>
       </c>
       <c r="R33" s="5" t="n"/>
-      <c r="T33" s="12" t="n"/>
-      <c r="U33" s="4" t="inlineStr">
+      <c r="T33" s="14" t="n"/>
+      <c r="U33" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="V33" s="5" t="n"/>
-      <c r="W33" s="4" t="inlineStr">
+      <c r="W33" s="12" t="inlineStr">
         <is>
           <t>主 -</t>
         </is>
       </c>
       <c r="X33" s="5" t="n"/>
-      <c r="Z33" s="12" t="n"/>
-      <c r="AA33" s="4" t="inlineStr">
+      <c r="Z33" s="14" t="n"/>
+      <c r="AA33" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="AB33" s="5" t="n"/>
-      <c r="AC33" s="4" t="inlineStr">
+      <c r="AC33" s="13" t="inlineStr">
         <is>
           <t>主 650</t>
         </is>
       </c>
       <c r="AD33" s="5" t="n"/>
     </row>
-    <row r="34" ht="20" customHeight="1">
+    <row r="34" ht="34" customHeight="1">
       <c r="B34" s="3" t="n"/>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="15" t="n"/>
       <c r="F34" s="5" t="n"/>
       <c r="H34" s="3" t="n"/>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="13" t="n"/>
+      <c r="I34" s="15" t="n"/>
+      <c r="J34" s="15" t="n"/>
+      <c r="K34" s="15" t="n"/>
       <c r="L34" s="5" t="n"/>
       <c r="N34" s="3" t="n"/>
-      <c r="O34" s="13" t="n"/>
-      <c r="P34" s="13" t="n"/>
-      <c r="Q34" s="13" t="n"/>
+      <c r="O34" s="15" t="n"/>
+      <c r="P34" s="15" t="n"/>
+      <c r="Q34" s="15" t="n"/>
       <c r="R34" s="5" t="n"/>
       <c r="T34" s="3" t="n"/>
-      <c r="U34" s="13" t="n"/>
-      <c r="V34" s="13" t="n"/>
-      <c r="W34" s="13" t="n"/>
+      <c r="U34" s="15" t="n"/>
+      <c r="V34" s="15" t="n"/>
+      <c r="W34" s="15" t="n"/>
       <c r="X34" s="5" t="n"/>
       <c r="Z34" s="3" t="n"/>
-      <c r="AA34" s="13" t="n"/>
-      <c r="AB34" s="13" t="n"/>
-      <c r="AC34" s="13" t="n"/>
+      <c r="AA34" s="15" t="n"/>
+      <c r="AB34" s="15" t="n"/>
+      <c r="AC34" s="15" t="n"/>
       <c r="AD34" s="5" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -9625,52 +9631,52 @@
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="B36" s="11" t="n"/>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="D36" s="5" t="n"/>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="F36" s="5" t="n"/>
       <c r="H36" s="11" t="n"/>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="I36" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="J36" s="5" t="n"/>
-      <c r="K36" s="4" t="inlineStr">
+      <c r="K36" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="N36" s="11" t="n"/>
-      <c r="O36" s="4" t="inlineStr">
+      <c r="O36" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="P36" s="5" t="n"/>
-      <c r="Q36" s="4" t="inlineStr">
+      <c r="Q36" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="R36" s="5" t="n"/>
       <c r="T36" s="11" t="n"/>
-      <c r="U36" s="4" t="inlineStr">
+      <c r="U36" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="V36" s="5" t="n"/>
-      <c r="W36" s="4" t="inlineStr">
+      <c r="W36" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
@@ -9683,107 +9689,107 @@
       <c r="AD36" s="5" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="D37" s="5" t="n"/>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>主 585</t>
         </is>
       </c>
       <c r="F37" s="5" t="n"/>
-      <c r="H37" s="12" t="n"/>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="13" t="inlineStr">
         <is>
           <t>副 1000/980</t>
         </is>
       </c>
       <c r="J37" s="5" t="n"/>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="K37" s="12" t="inlineStr">
         <is>
           <t>主 -</t>
         </is>
       </c>
       <c r="L37" s="5" t="n"/>
-      <c r="N37" s="12" t="n"/>
-      <c r="O37" s="4" t="inlineStr">
+      <c r="N37" s="14" t="n"/>
+      <c r="O37" s="13" t="inlineStr">
         <is>
           <t>副 765</t>
         </is>
       </c>
       <c r="P37" s="5" t="n"/>
-      <c r="Q37" s="4" t="inlineStr">
+      <c r="Q37" s="13" t="inlineStr">
         <is>
           <t>主 675/650</t>
         </is>
       </c>
       <c r="R37" s="5" t="n"/>
-      <c r="T37" s="12" t="n"/>
-      <c r="U37" s="4" t="inlineStr">
+      <c r="T37" s="14" t="n"/>
+      <c r="U37" s="13" t="inlineStr">
         <is>
           <t>副 765</t>
         </is>
       </c>
       <c r="V37" s="5" t="n"/>
-      <c r="W37" s="4" t="inlineStr">
+      <c r="W37" s="13" t="inlineStr">
         <is>
           <t>主 670</t>
         </is>
       </c>
       <c r="X37" s="5" t="n"/>
-      <c r="Z37" s="12" t="n"/>
+      <c r="Z37" s="14" t="n"/>
       <c r="AA37" s="3" t="n"/>
       <c r="AB37" s="5" t="n"/>
       <c r="AC37" s="3" t="n"/>
       <c r="AD37" s="5" t="n"/>
     </row>
-    <row r="38" ht="20" customHeight="1">
+    <row r="38" ht="34" customHeight="1">
       <c r="B38" s="3" t="n"/>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="n"/>
       <c r="F38" s="5" t="n"/>
       <c r="H38" s="3" t="n"/>
-      <c r="I38" s="13" t="n"/>
-      <c r="J38" s="13" t="n"/>
-      <c r="K38" s="13" t="n"/>
+      <c r="I38" s="15" t="n"/>
+      <c r="J38" s="15" t="n"/>
+      <c r="K38" s="15" t="n"/>
       <c r="L38" s="5" t="n"/>
       <c r="N38" s="3" t="n"/>
-      <c r="O38" s="13" t="n"/>
-      <c r="P38" s="13" t="n"/>
-      <c r="Q38" s="13" t="n"/>
+      <c r="O38" s="15" t="n"/>
+      <c r="P38" s="15" t="n"/>
+      <c r="Q38" s="15" t="n"/>
       <c r="R38" s="5" t="n"/>
       <c r="T38" s="3" t="n"/>
-      <c r="U38" s="13" t="n"/>
-      <c r="V38" s="13" t="n"/>
-      <c r="W38" s="13" t="n"/>
+      <c r="U38" s="15" t="n"/>
+      <c r="V38" s="15" t="n"/>
+      <c r="W38" s="15" t="n"/>
       <c r="X38" s="5" t="n"/>
       <c r="Z38" s="3" t="n"/>
-      <c r="AA38" s="13" t="n"/>
-      <c r="AB38" s="13" t="n"/>
-      <c r="AC38" s="13" t="n"/>
+      <c r="AA38" s="15" t="n"/>
+      <c r="AB38" s="15" t="n"/>
+      <c r="AC38" s="15" t="n"/>
       <c r="AD38" s="5" t="n"/>
     </row>
     <row r="40" ht="27" customHeight="1">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>评分来源：Athieno《OFFICIAL Operator Tier List in Y11S2》｜Y11S2｜覆盖至 Y11S2（2026-06-02）｜发布 2026-06-02｜采集 2026-07-25T00:00:00+08:00</t>
         </is>
       </c>
     </row>
     <row r="41" ht="27" customHeight="1">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>游戏数据：灰机 Wiki｜Y11S2 系统覆盖行动｜Y11S2.2｜抓取 2026-07-26T13:13:13.429371+08:00｜除评分外，其他信息均为该时间点的最新数据</t>
         </is>
       </c>
     </row>
     <row r="42" ht="27" customHeight="1">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>补丁区间：评分覆盖至 2026-06-02；Wiki 数据截至 2026-07-26；Y11S2.1（2026-06-23）→ Y11S2.2（2026-07-14）</t>
         </is>
@@ -10271,65 +10277,65 @@
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="B4" s="11" t="n"/>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="D4" s="5" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="F4" s="5" t="n"/>
       <c r="H4" s="11" t="n"/>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="J4" s="5" t="n"/>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="L4" s="5" t="n"/>
       <c r="N4" s="11" t="n"/>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O4" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="P4" s="5" t="n"/>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="Q4" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="R4" s="5" t="n"/>
       <c r="T4" s="11" t="n"/>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="U4" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="V4" s="5" t="n"/>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="W4" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="X4" s="5" t="n"/>
       <c r="Z4" s="11" t="n"/>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AA4" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="AB4" s="5" t="n"/>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AC4" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
@@ -10337,97 +10343,97 @@
       <c r="AD4" s="5" t="n"/>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="B5" s="12" t="n"/>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>主 1200</t>
         </is>
       </c>
       <c r="F5" s="5" t="n"/>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="H5" s="14" t="n"/>
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="J5" s="5" t="n"/>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="K5" s="13" t="inlineStr">
         <is>
           <t>主 980</t>
         </is>
       </c>
       <c r="L5" s="5" t="n"/>
-      <c r="N5" s="12" t="n"/>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="N5" s="14" t="n"/>
+      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="Q5" s="13" t="inlineStr">
         <is>
           <t>主 900</t>
         </is>
       </c>
       <c r="R5" s="5" t="n"/>
-      <c r="T5" s="12" t="n"/>
-      <c r="U5" s="4" t="inlineStr">
+      <c r="T5" s="14" t="n"/>
+      <c r="U5" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="V5" s="5" t="n"/>
-      <c r="W5" s="4" t="inlineStr">
+      <c r="W5" s="13" t="inlineStr">
         <is>
           <t>主 1200</t>
         </is>
       </c>
       <c r="X5" s="5" t="n"/>
-      <c r="Z5" s="12" t="n"/>
-      <c r="AA5" s="4" t="inlineStr">
+      <c r="Z5" s="14" t="n"/>
+      <c r="AA5" s="13" t="inlineStr">
         <is>
           <t>副 1270</t>
         </is>
       </c>
       <c r="AB5" s="5" t="n"/>
-      <c r="AC5" s="4" t="inlineStr">
+      <c r="AC5" s="13" t="inlineStr">
         <is>
           <t>主 970</t>
         </is>
       </c>
       <c r="AD5" s="5" t="n"/>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6" ht="34" customHeight="1">
       <c r="B6" s="3" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
       <c r="F6" s="5" t="n"/>
       <c r="H6" s="3" t="n"/>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="13" t="n"/>
-      <c r="K6" s="13" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
+      <c r="K6" s="15" t="n"/>
       <c r="L6" s="5" t="n"/>
       <c r="N6" s="3" t="n"/>
-      <c r="O6" s="13" t="n"/>
-      <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="13" t="n"/>
+      <c r="O6" s="15" t="n"/>
+      <c r="P6" s="15" t="n"/>
+      <c r="Q6" s="15" t="n"/>
       <c r="R6" s="5" t="n"/>
       <c r="T6" s="3" t="n"/>
-      <c r="U6" s="13" t="n"/>
-      <c r="V6" s="13" t="n"/>
-      <c r="W6" s="13" t="n"/>
+      <c r="U6" s="15" t="n"/>
+      <c r="V6" s="15" t="n"/>
+      <c r="W6" s="15" t="n"/>
       <c r="X6" s="5" t="n"/>
       <c r="Z6" s="3" t="n"/>
-      <c r="AA6" s="13" t="n"/>
-      <c r="AB6" s="13" t="n"/>
-      <c r="AC6" s="13" t="n"/>
+      <c r="AA6" s="15" t="n"/>
+      <c r="AB6" s="15" t="n"/>
+      <c r="AC6" s="15" t="n"/>
       <c r="AD6" s="5" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -10519,65 +10525,65 @@
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="B8" s="11" t="n"/>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="D8" s="5" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="F8" s="5" t="n"/>
       <c r="H8" s="11" t="n"/>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="J8" s="5" t="n"/>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="K8" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="L8" s="5" t="n"/>
       <c r="N8" s="11" t="n"/>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="O8" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="Q8" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="R8" s="5" t="n"/>
       <c r="T8" s="11" t="n"/>
-      <c r="U8" s="4" t="inlineStr">
+      <c r="U8" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="V8" s="5" t="n"/>
-      <c r="W8" s="4" t="inlineStr">
+      <c r="W8" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="X8" s="5" t="n"/>
       <c r="Z8" s="11" t="n"/>
-      <c r="AA8" s="4" t="inlineStr">
+      <c r="AA8" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="AB8" s="5" t="n"/>
-      <c r="AC8" s="4" t="inlineStr">
+      <c r="AC8" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
@@ -10585,97 +10591,97 @@
       <c r="AD8" s="5" t="n"/>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>主 1080</t>
         </is>
       </c>
       <c r="F9" s="5" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="H9" s="14" t="n"/>
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="J9" s="5" t="n"/>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>主 1080/800</t>
         </is>
       </c>
       <c r="L9" s="5" t="n"/>
-      <c r="N9" s="12" t="n"/>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="N9" s="14" t="n"/>
+      <c r="O9" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="Q9" s="13" t="inlineStr">
         <is>
           <t>主 980/780</t>
         </is>
       </c>
       <c r="R9" s="5" t="n"/>
-      <c r="T9" s="12" t="n"/>
-      <c r="U9" s="4" t="inlineStr">
+      <c r="T9" s="14" t="n"/>
+      <c r="U9" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="V9" s="5" t="n"/>
-      <c r="W9" s="4" t="inlineStr">
+      <c r="W9" s="13" t="inlineStr">
         <is>
           <t>主 900</t>
         </is>
       </c>
       <c r="X9" s="5" t="n"/>
-      <c r="Z9" s="12" t="n"/>
-      <c r="AA9" s="4" t="inlineStr">
+      <c r="Z9" s="14" t="n"/>
+      <c r="AA9" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="AB9" s="5" t="n"/>
-      <c r="AC9" s="4" t="inlineStr">
+      <c r="AC9" s="13" t="inlineStr">
         <is>
           <t>主 900</t>
         </is>
       </c>
       <c r="AD9" s="5" t="n"/>
     </row>
-    <row r="10" ht="20" customHeight="1">
+    <row r="10" ht="34" customHeight="1">
       <c r="B10" s="3" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="H10" s="3" t="n"/>
-      <c r="I10" s="13" t="n"/>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="13" t="n"/>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="15" t="n"/>
+      <c r="K10" s="15" t="n"/>
       <c r="L10" s="5" t="n"/>
       <c r="N10" s="3" t="n"/>
-      <c r="O10" s="13" t="n"/>
-      <c r="P10" s="13" t="n"/>
-      <c r="Q10" s="13" t="n"/>
+      <c r="O10" s="15" t="n"/>
+      <c r="P10" s="15" t="n"/>
+      <c r="Q10" s="15" t="n"/>
       <c r="R10" s="5" t="n"/>
       <c r="T10" s="3" t="n"/>
-      <c r="U10" s="13" t="n"/>
-      <c r="V10" s="13" t="n"/>
-      <c r="W10" s="13" t="n"/>
+      <c r="U10" s="15" t="n"/>
+      <c r="V10" s="15" t="n"/>
+      <c r="W10" s="15" t="n"/>
       <c r="X10" s="5" t="n"/>
       <c r="Z10" s="3" t="n"/>
-      <c r="AA10" s="13" t="n"/>
-      <c r="AB10" s="13" t="n"/>
-      <c r="AC10" s="13" t="n"/>
+      <c r="AA10" s="15" t="n"/>
+      <c r="AB10" s="15" t="n"/>
+      <c r="AC10" s="15" t="n"/>
       <c r="AD10" s="5" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -10720,7 +10726,7 @@
         </is>
       </c>
       <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="15" t="inlineStr">
+      <c r="Q11" s="17" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -10737,7 +10743,7 @@
         </is>
       </c>
       <c r="V11" s="5" t="n"/>
-      <c r="W11" s="15" t="inlineStr">
+      <c r="W11" s="17" t="inlineStr">
         <is>
           <t>F+</t>
         </is>
@@ -10754,7 +10760,7 @@
         </is>
       </c>
       <c r="AB11" s="5" t="n"/>
-      <c r="AC11" s="15" t="inlineStr">
+      <c r="AC11" s="17" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -10767,65 +10773,65 @@
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="B12" s="11" t="n"/>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="D12" s="5" t="n"/>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="F12" s="5" t="n"/>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="J12" s="5" t="n"/>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K12" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="L12" s="5" t="n"/>
       <c r="N12" s="11" t="n"/>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="O12" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="4" t="inlineStr">
+      <c r="Q12" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="R12" s="5" t="n"/>
       <c r="T12" s="11" t="n"/>
-      <c r="U12" s="4" t="inlineStr">
+      <c r="U12" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="V12" s="5" t="n"/>
-      <c r="W12" s="4" t="inlineStr">
+      <c r="W12" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="X12" s="5" t="n"/>
       <c r="Z12" s="11" t="n"/>
-      <c r="AA12" s="4" t="inlineStr">
+      <c r="AA12" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="AB12" s="5" t="n"/>
-      <c r="AC12" s="4" t="inlineStr">
+      <c r="AC12" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
@@ -10833,101 +10839,101 @@
       <c r="AD12" s="5" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>副 765</t>
         </is>
       </c>
       <c r="D13" s="5" t="n"/>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>主 900</t>
         </is>
       </c>
       <c r="F13" s="5" t="n"/>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="H13" s="14" t="n"/>
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="J13" s="5" t="n"/>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K13" s="13" t="inlineStr">
         <is>
           <t>主 900/300</t>
         </is>
       </c>
       <c r="L13" s="5" t="n"/>
-      <c r="N13" s="12" t="n"/>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="N13" s="14" t="n"/>
+      <c r="O13" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="Q13" s="13" t="inlineStr">
         <is>
           <t>主 950/300</t>
         </is>
       </c>
       <c r="R13" s="5" t="n"/>
-      <c r="T13" s="12" t="n"/>
-      <c r="U13" s="4" t="inlineStr">
+      <c r="T13" s="14" t="n"/>
+      <c r="U13" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="V13" s="5" t="n"/>
-      <c r="W13" s="4" t="inlineStr">
+      <c r="W13" s="13" t="inlineStr">
         <is>
           <t>主 970/800</t>
         </is>
       </c>
       <c r="X13" s="5" t="n"/>
-      <c r="Z13" s="12" t="n"/>
-      <c r="AA13" s="4" t="inlineStr">
+      <c r="Z13" s="14" t="n"/>
+      <c r="AA13" s="13" t="inlineStr">
         <is>
           <t>副 765</t>
         </is>
       </c>
       <c r="AB13" s="5" t="n"/>
-      <c r="AC13" s="4" t="inlineStr">
+      <c r="AC13" s="13" t="inlineStr">
         <is>
           <t>主 970/800</t>
         </is>
       </c>
       <c r="AD13" s="5" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
+    <row r="14" ht="34" customHeight="1">
       <c r="B14" s="3" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="H14" s="3" t="n"/>
-      <c r="I14" s="13" t="n"/>
-      <c r="J14" s="13" t="n"/>
-      <c r="K14" s="13" t="n"/>
+      <c r="I14" s="15" t="n"/>
+      <c r="J14" s="15" t="n"/>
+      <c r="K14" s="15" t="n"/>
       <c r="L14" s="5" t="n"/>
       <c r="N14" s="3" t="n"/>
-      <c r="O14" s="13" t="n"/>
-      <c r="P14" s="13" t="n"/>
-      <c r="Q14" s="13" t="n"/>
+      <c r="O14" s="15" t="n"/>
+      <c r="P14" s="15" t="n"/>
+      <c r="Q14" s="15" t="n"/>
       <c r="R14" s="5" t="n"/>
       <c r="T14" s="3" t="n"/>
-      <c r="U14" s="13" t="n"/>
-      <c r="V14" s="13" t="n"/>
-      <c r="W14" s="13" t="n"/>
+      <c r="U14" s="15" t="n"/>
+      <c r="V14" s="15" t="n"/>
+      <c r="W14" s="15" t="n"/>
       <c r="X14" s="5" t="n"/>
       <c r="Z14" s="3" t="n"/>
-      <c r="AA14" s="13" t="n"/>
-      <c r="AB14" s="13" t="n"/>
-      <c r="AC14" s="13" t="n"/>
+      <c r="AA14" s="15" t="n"/>
+      <c r="AB14" s="15" t="n"/>
+      <c r="AC14" s="15" t="n"/>
       <c r="AD14" s="5" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
@@ -11020,65 +11026,65 @@
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="B16" s="11" t="n"/>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="D16" s="5" t="n"/>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="F16" s="5" t="n"/>
       <c r="H16" s="11" t="n"/>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="J16" s="5" t="n"/>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K16" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="N16" s="11" t="n"/>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="O16" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="P16" s="5" t="n"/>
-      <c r="Q16" s="4" t="inlineStr">
+      <c r="Q16" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="R16" s="5" t="n"/>
       <c r="T16" s="11" t="n"/>
-      <c r="U16" s="4" t="inlineStr">
+      <c r="U16" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="V16" s="5" t="n"/>
-      <c r="W16" s="4" t="inlineStr">
+      <c r="W16" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="X16" s="5" t="n"/>
       <c r="Z16" s="11" t="n"/>
-      <c r="AA16" s="4" t="inlineStr">
+      <c r="AA16" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="AB16" s="5" t="n"/>
-      <c r="AC16" s="4" t="inlineStr">
+      <c r="AC16" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
@@ -11086,97 +11092,97 @@
       <c r="AD16" s="5" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>主 830</t>
         </is>
       </c>
       <c r="F17" s="5" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="13" t="inlineStr">
         <is>
           <t>副 1270</t>
         </is>
       </c>
       <c r="J17" s="5" t="n"/>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K17" s="13" t="inlineStr">
         <is>
           <t>主 800</t>
         </is>
       </c>
       <c r="L17" s="5" t="n"/>
-      <c r="N17" s="12" t="n"/>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="N17" s="14" t="n"/>
+      <c r="O17" s="13" t="inlineStr">
         <is>
           <t>副 1270</t>
         </is>
       </c>
       <c r="P17" s="5" t="n"/>
-      <c r="Q17" s="4" t="inlineStr">
+      <c r="Q17" s="13" t="inlineStr">
         <is>
           <t>主 830</t>
         </is>
       </c>
       <c r="R17" s="5" t="n"/>
-      <c r="T17" s="12" t="n"/>
-      <c r="U17" s="4" t="inlineStr">
+      <c r="T17" s="14" t="n"/>
+      <c r="U17" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="V17" s="5" t="n"/>
-      <c r="W17" s="4" t="inlineStr">
+      <c r="W17" s="13" t="inlineStr">
         <is>
           <t>主 800/720</t>
         </is>
       </c>
       <c r="X17" s="5" t="n"/>
-      <c r="Z17" s="12" t="n"/>
-      <c r="AA17" s="4" t="inlineStr">
+      <c r="Z17" s="14" t="n"/>
+      <c r="AA17" s="13" t="inlineStr">
         <is>
           <t>副 1270</t>
         </is>
       </c>
       <c r="AB17" s="5" t="n"/>
-      <c r="AC17" s="4" t="inlineStr">
+      <c r="AC17" s="13" t="inlineStr">
         <is>
           <t>主 800</t>
         </is>
       </c>
       <c r="AD17" s="5" t="n"/>
     </row>
-    <row r="18" ht="20" customHeight="1">
+    <row r="18" ht="34" customHeight="1">
       <c r="B18" s="3" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="H18" s="3" t="n"/>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="13" t="n"/>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="15" t="n"/>
+      <c r="K18" s="15" t="n"/>
       <c r="L18" s="5" t="n"/>
       <c r="N18" s="3" t="n"/>
-      <c r="O18" s="13" t="n"/>
-      <c r="P18" s="13" t="n"/>
-      <c r="Q18" s="13" t="n"/>
+      <c r="O18" s="15" t="n"/>
+      <c r="P18" s="15" t="n"/>
+      <c r="Q18" s="15" t="n"/>
       <c r="R18" s="5" t="n"/>
       <c r="T18" s="3" t="n"/>
-      <c r="U18" s="13" t="n"/>
-      <c r="V18" s="13" t="n"/>
-      <c r="W18" s="13" t="n"/>
+      <c r="U18" s="15" t="n"/>
+      <c r="V18" s="15" t="n"/>
+      <c r="W18" s="15" t="n"/>
       <c r="X18" s="5" t="n"/>
       <c r="Z18" s="3" t="n"/>
-      <c r="AA18" s="13" t="n"/>
-      <c r="AB18" s="13" t="n"/>
-      <c r="AC18" s="13" t="n"/>
+      <c r="AA18" s="15" t="n"/>
+      <c r="AB18" s="15" t="n"/>
+      <c r="AC18" s="15" t="n"/>
       <c r="AD18" s="5" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -11256,52 +11262,52 @@
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="B20" s="11" t="n"/>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="F20" s="5" t="n"/>
       <c r="H20" s="11" t="n"/>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I20" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="J20" s="5" t="n"/>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K20" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="N20" s="11" t="n"/>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="O20" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="4" t="inlineStr">
+      <c r="Q20" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="R20" s="5" t="n"/>
       <c r="T20" s="11" t="n"/>
-      <c r="U20" s="4" t="inlineStr">
+      <c r="U20" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="V20" s="5" t="n"/>
-      <c r="W20" s="4" t="inlineStr">
+      <c r="W20" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
@@ -11314,93 +11320,93 @@
       <c r="AD20" s="5" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="D21" s="5" t="n"/>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>主 830</t>
         </is>
       </c>
       <c r="F21" s="5" t="n"/>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="13" t="inlineStr">
         <is>
           <t>副 1000</t>
         </is>
       </c>
       <c r="J21" s="5" t="n"/>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K21" s="13" t="inlineStr">
         <is>
           <t>主 780</t>
         </is>
       </c>
       <c r="L21" s="5" t="n"/>
-      <c r="N21" s="12" t="n"/>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="N21" s="14" t="n"/>
+      <c r="O21" s="13" t="inlineStr">
         <is>
           <t>副 1100</t>
         </is>
       </c>
       <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="4" t="inlineStr">
+      <c r="Q21" s="13" t="inlineStr">
         <is>
           <t>主 800</t>
         </is>
       </c>
       <c r="R21" s="5" t="n"/>
-      <c r="T21" s="12" t="n"/>
-      <c r="U21" s="4" t="inlineStr">
+      <c r="T21" s="14" t="n"/>
+      <c r="U21" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="V21" s="5" t="n"/>
-      <c r="W21" s="4" t="inlineStr">
+      <c r="W21" s="13" t="inlineStr">
         <is>
           <t>主 800</t>
         </is>
       </c>
       <c r="X21" s="5" t="n"/>
-      <c r="Z21" s="12" t="n"/>
+      <c r="Z21" s="14" t="n"/>
       <c r="AA21" s="3" t="n"/>
       <c r="AB21" s="5" t="n"/>
       <c r="AC21" s="3" t="n"/>
       <c r="AD21" s="5" t="n"/>
     </row>
-    <row r="22" ht="40" customHeight="1">
+    <row r="22" ht="34" customHeight="1">
       <c r="B22" s="3" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="H22" s="3" t="n"/>
-      <c r="I22" s="13" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="13" t="n"/>
+      <c r="I22" s="15" t="n"/>
+      <c r="J22" s="15" t="n"/>
+      <c r="K22" s="15" t="n"/>
       <c r="L22" s="5" t="n"/>
       <c r="N22" s="3" t="n"/>
-      <c r="O22" s="13" t="n"/>
-      <c r="P22" s="13" t="n"/>
-      <c r="Q22" s="13" t="n"/>
+      <c r="O22" s="15" t="n"/>
+      <c r="P22" s="15" t="n"/>
+      <c r="Q22" s="15" t="n"/>
       <c r="R22" s="5" t="n"/>
       <c r="T22" s="3" t="n"/>
-      <c r="U22" s="13" t="n"/>
-      <c r="V22" s="13" t="n"/>
-      <c r="W22" s="13" t="n"/>
+      <c r="U22" s="15" t="n"/>
+      <c r="V22" s="15" t="n"/>
+      <c r="W22" s="15" t="n"/>
       <c r="X22" s="5" t="n"/>
       <c r="Z22" s="3" t="n"/>
-      <c r="AA22" s="13" t="n"/>
-      <c r="AB22" s="13" t="n"/>
-      <c r="AC22" s="13" t="n"/>
+      <c r="AA22" s="15" t="n"/>
+      <c r="AB22" s="15" t="n"/>
+      <c r="AC22" s="15" t="n"/>
       <c r="AD22" s="5" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
@@ -11493,65 +11499,65 @@
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="B24" s="11" t="n"/>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="D24" s="5" t="n"/>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="F24" s="5" t="n"/>
       <c r="H24" s="11" t="n"/>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="J24" s="5" t="n"/>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K24" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="L24" s="5" t="n"/>
       <c r="N24" s="11" t="n"/>
-      <c r="O24" s="4" t="inlineStr">
+      <c r="O24" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="4" t="inlineStr">
+      <c r="Q24" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="R24" s="5" t="n"/>
       <c r="T24" s="11" t="n"/>
-      <c r="U24" s="4" t="inlineStr">
+      <c r="U24" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="V24" s="5" t="n"/>
-      <c r="W24" s="4" t="inlineStr">
+      <c r="W24" s="13" t="inlineStr">
         <is>
           <t>主狙 ✓</t>
         </is>
       </c>
       <c r="X24" s="5" t="n"/>
       <c r="Z24" s="11" t="n"/>
-      <c r="AA24" s="4" t="inlineStr">
+      <c r="AA24" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="AB24" s="5" t="n"/>
-      <c r="AC24" s="4" t="inlineStr">
+      <c r="AC24" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
@@ -11559,97 +11565,97 @@
       <c r="AD24" s="5" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>副 1000</t>
         </is>
       </c>
       <c r="D25" s="5" t="n"/>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>主 700</t>
         </is>
       </c>
       <c r="F25" s="5" t="n"/>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="H25" s="14" t="n"/>
+      <c r="I25" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="J25" s="5" t="n"/>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="K25" s="13" t="inlineStr">
         <is>
           <t>主 750/300</t>
         </is>
       </c>
       <c r="L25" s="5" t="n"/>
-      <c r="N25" s="12" t="n"/>
-      <c r="O25" s="4" t="inlineStr">
+      <c r="N25" s="14" t="n"/>
+      <c r="O25" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="4" t="inlineStr">
+      <c r="Q25" s="13" t="inlineStr">
         <is>
           <t>主 700</t>
         </is>
       </c>
       <c r="R25" s="5" t="n"/>
-      <c r="T25" s="12" t="n"/>
-      <c r="U25" s="4" t="inlineStr">
+      <c r="T25" s="14" t="n"/>
+      <c r="U25" s="13" t="inlineStr">
         <is>
           <t>副 1270/1000</t>
         </is>
       </c>
       <c r="V25" s="5" t="n"/>
-      <c r="W25" s="4" t="inlineStr">
+      <c r="W25" s="13" t="inlineStr">
         <is>
           <t>主 720</t>
         </is>
       </c>
       <c r="X25" s="5" t="n"/>
-      <c r="Z25" s="12" t="n"/>
-      <c r="AA25" s="4" t="inlineStr">
+      <c r="Z25" s="14" t="n"/>
+      <c r="AA25" s="13" t="inlineStr">
         <is>
           <t>副 1100</t>
         </is>
       </c>
       <c r="AB25" s="5" t="n"/>
-      <c r="AC25" s="4" t="inlineStr">
+      <c r="AC25" s="13" t="inlineStr">
         <is>
           <t>主 750/550</t>
         </is>
       </c>
       <c r="AD25" s="5" t="n"/>
     </row>
-    <row r="26" ht="20" customHeight="1">
+    <row r="26" ht="34" customHeight="1">
       <c r="B26" s="3" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="H26" s="3" t="n"/>
-      <c r="I26" s="13" t="n"/>
-      <c r="J26" s="13" t="n"/>
-      <c r="K26" s="13" t="n"/>
+      <c r="I26" s="15" t="n"/>
+      <c r="J26" s="15" t="n"/>
+      <c r="K26" s="15" t="n"/>
       <c r="L26" s="5" t="n"/>
       <c r="N26" s="3" t="n"/>
-      <c r="O26" s="13" t="n"/>
-      <c r="P26" s="13" t="n"/>
-      <c r="Q26" s="13" t="n"/>
+      <c r="O26" s="15" t="n"/>
+      <c r="P26" s="15" t="n"/>
+      <c r="Q26" s="15" t="n"/>
       <c r="R26" s="5" t="n"/>
       <c r="T26" s="3" t="n"/>
-      <c r="U26" s="13" t="n"/>
-      <c r="V26" s="13" t="n"/>
-      <c r="W26" s="13" t="n"/>
+      <c r="U26" s="15" t="n"/>
+      <c r="V26" s="15" t="n"/>
+      <c r="W26" s="15" t="n"/>
       <c r="X26" s="5" t="n"/>
       <c r="Z26" s="3" t="n"/>
-      <c r="AA26" s="13" t="n"/>
-      <c r="AB26" s="13" t="n"/>
-      <c r="AC26" s="13" t="n"/>
+      <c r="AA26" s="15" t="n"/>
+      <c r="AB26" s="15" t="n"/>
+      <c r="AC26" s="15" t="n"/>
       <c r="AD26" s="5" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -11711,7 +11717,7 @@
         </is>
       </c>
       <c r="V27" s="5" t="n"/>
-      <c r="W27" s="15" t="inlineStr">
+      <c r="W27" s="17" t="inlineStr">
         <is>
           <t>F+</t>
         </is>
@@ -11729,52 +11735,52 @@
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="B28" s="11" t="n"/>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="D28" s="5" t="n"/>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="F28" s="5" t="n"/>
       <c r="H28" s="11" t="n"/>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="I28" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="J28" s="5" t="n"/>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="K28" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="L28" s="5" t="n"/>
       <c r="N28" s="11" t="n"/>
-      <c r="O28" s="4" t="inlineStr">
+      <c r="O28" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="P28" s="5" t="n"/>
-      <c r="Q28" s="4" t="inlineStr">
+      <c r="Q28" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="R28" s="5" t="n"/>
       <c r="T28" s="11" t="n"/>
-      <c r="U28" s="4" t="inlineStr">
+      <c r="U28" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="V28" s="5" t="n"/>
-      <c r="W28" s="4" t="inlineStr">
+      <c r="W28" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
@@ -11787,93 +11793,93 @@
       <c r="AD28" s="5" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="D29" s="5" t="n"/>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>主 745</t>
         </is>
       </c>
       <c r="F29" s="5" t="n"/>
-      <c r="H29" s="12" t="n"/>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="J29" s="5" t="n"/>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="K29" s="13" t="inlineStr">
         <is>
           <t>主 740</t>
         </is>
       </c>
       <c r="L29" s="5" t="n"/>
-      <c r="N29" s="12" t="n"/>
-      <c r="O29" s="4" t="inlineStr">
+      <c r="N29" s="14" t="n"/>
+      <c r="O29" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="P29" s="5" t="n"/>
-      <c r="Q29" s="4" t="inlineStr">
+      <c r="Q29" s="13" t="inlineStr">
         <is>
           <t>主 750</t>
         </is>
       </c>
       <c r="R29" s="5" t="n"/>
-      <c r="T29" s="12" t="n"/>
-      <c r="U29" s="4" t="inlineStr">
+      <c r="T29" s="14" t="n"/>
+      <c r="U29" s="13" t="inlineStr">
         <is>
           <t>副 1100</t>
         </is>
       </c>
       <c r="V29" s="5" t="n"/>
-      <c r="W29" s="4" t="inlineStr">
+      <c r="W29" s="13" t="inlineStr">
         <is>
           <t>主 700</t>
         </is>
       </c>
       <c r="X29" s="5" t="n"/>
-      <c r="Z29" s="12" t="n"/>
+      <c r="Z29" s="14" t="n"/>
       <c r="AA29" s="3" t="n"/>
       <c r="AB29" s="5" t="n"/>
       <c r="AC29" s="3" t="n"/>
       <c r="AD29" s="5" t="n"/>
     </row>
-    <row r="30" ht="20" customHeight="1">
+    <row r="30" ht="34" customHeight="1">
       <c r="B30" s="3" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
       <c r="F30" s="5" t="n"/>
       <c r="H30" s="3" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="13" t="n"/>
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="15" t="n"/>
+      <c r="K30" s="15" t="n"/>
       <c r="L30" s="5" t="n"/>
       <c r="N30" s="3" t="n"/>
-      <c r="O30" s="13" t="n"/>
-      <c r="P30" s="13" t="n"/>
-      <c r="Q30" s="13" t="n"/>
+      <c r="O30" s="15" t="n"/>
+      <c r="P30" s="15" t="n"/>
+      <c r="Q30" s="15" t="n"/>
       <c r="R30" s="5" t="n"/>
       <c r="T30" s="3" t="n"/>
-      <c r="U30" s="13" t="n"/>
-      <c r="V30" s="13" t="n"/>
-      <c r="W30" s="13" t="n"/>
+      <c r="U30" s="15" t="n"/>
+      <c r="V30" s="15" t="n"/>
+      <c r="W30" s="15" t="n"/>
       <c r="X30" s="5" t="n"/>
       <c r="Z30" s="3" t="n"/>
-      <c r="AA30" s="13" t="n"/>
-      <c r="AB30" s="13" t="n"/>
-      <c r="AC30" s="13" t="n"/>
+      <c r="AA30" s="15" t="n"/>
+      <c r="AB30" s="15" t="n"/>
+      <c r="AC30" s="15" t="n"/>
       <c r="AD30" s="5" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>Ⅳ</t>
         </is>
@@ -11936,7 +11942,7 @@
         </is>
       </c>
       <c r="V31" s="5" t="n"/>
-      <c r="W31" s="19" t="inlineStr">
+      <c r="W31" s="21" t="inlineStr">
         <is>
           <t>D+</t>
         </is>
@@ -11953,7 +11959,7 @@
         </is>
       </c>
       <c r="AB31" s="5" t="n"/>
-      <c r="AC31" s="15" t="inlineStr">
+      <c r="AC31" s="17" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -11966,65 +11972,65 @@
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="B32" s="11" t="n"/>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="D32" s="5" t="n"/>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="F32" s="5" t="n"/>
       <c r="H32" s="11" t="n"/>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="I32" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="J32" s="5" t="n"/>
-      <c r="K32" s="4" t="inlineStr">
+      <c r="K32" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="L32" s="5" t="n"/>
       <c r="N32" s="11" t="n"/>
-      <c r="O32" s="4" t="inlineStr">
+      <c r="O32" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="P32" s="5" t="n"/>
-      <c r="Q32" s="4" t="inlineStr">
+      <c r="Q32" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="R32" s="5" t="n"/>
       <c r="T32" s="11" t="n"/>
-      <c r="U32" s="4" t="inlineStr">
+      <c r="U32" s="13" t="inlineStr">
         <is>
           <t>副喷 ✓</t>
         </is>
       </c>
       <c r="V32" s="5" t="n"/>
-      <c r="W32" s="4" t="inlineStr">
+      <c r="W32" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
       </c>
       <c r="X32" s="5" t="n"/>
       <c r="Z32" s="11" t="n"/>
-      <c r="AA32" s="4" t="inlineStr">
+      <c r="AA32" s="12" t="inlineStr">
         <is>
           <t>副喷 -</t>
         </is>
       </c>
       <c r="AB32" s="5" t="n"/>
-      <c r="AC32" s="4" t="inlineStr">
+      <c r="AC32" s="12" t="inlineStr">
         <is>
           <t>主狙 -</t>
         </is>
@@ -12032,115 +12038,115 @@
       <c r="AD32" s="5" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>副 980</t>
         </is>
       </c>
       <c r="D33" s="5" t="n"/>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>主 -</t>
         </is>
       </c>
       <c r="F33" s="5" t="n"/>
-      <c r="H33" s="12" t="n"/>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="H33" s="14" t="n"/>
+      <c r="I33" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="J33" s="5" t="n"/>
-      <c r="K33" s="4" t="inlineStr">
+      <c r="K33" s="13" t="inlineStr">
         <is>
           <t>主 600</t>
         </is>
       </c>
       <c r="L33" s="5" t="n"/>
-      <c r="N33" s="12" t="n"/>
-      <c r="O33" s="4" t="inlineStr">
+      <c r="N33" s="14" t="n"/>
+      <c r="O33" s="13" t="inlineStr">
         <is>
           <t>副 765</t>
         </is>
       </c>
       <c r="P33" s="5" t="n"/>
-      <c r="Q33" s="4" t="inlineStr">
+      <c r="Q33" s="13" t="inlineStr">
         <is>
           <t>主 600</t>
         </is>
       </c>
       <c r="R33" s="5" t="n"/>
-      <c r="T33" s="12" t="n"/>
-      <c r="U33" s="4" t="inlineStr">
+      <c r="T33" s="14" t="n"/>
+      <c r="U33" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="V33" s="5" t="n"/>
-      <c r="W33" s="4" t="inlineStr">
+      <c r="W33" s="13" t="inlineStr">
         <is>
           <t>主 575</t>
         </is>
       </c>
       <c r="X33" s="5" t="n"/>
-      <c r="Z33" s="12" t="n"/>
-      <c r="AA33" s="4" t="inlineStr">
+      <c r="Z33" s="14" t="n"/>
+      <c r="AA33" s="12" t="inlineStr">
         <is>
           <t>副 -</t>
         </is>
       </c>
       <c r="AB33" s="5" t="n"/>
-      <c r="AC33" s="4" t="inlineStr">
+      <c r="AC33" s="13" t="inlineStr">
         <is>
           <t>主 550</t>
         </is>
       </c>
       <c r="AD33" s="5" t="n"/>
     </row>
-    <row r="34" ht="20" customHeight="1">
+    <row r="34" ht="34" customHeight="1">
       <c r="B34" s="3" t="n"/>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="15" t="n"/>
       <c r="F34" s="5" t="n"/>
       <c r="H34" s="3" t="n"/>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="13" t="n"/>
+      <c r="I34" s="15" t="n"/>
+      <c r="J34" s="15" t="n"/>
+      <c r="K34" s="15" t="n"/>
       <c r="L34" s="5" t="n"/>
       <c r="N34" s="3" t="n"/>
-      <c r="O34" s="13" t="n"/>
-      <c r="P34" s="13" t="n"/>
-      <c r="Q34" s="13" t="n"/>
+      <c r="O34" s="15" t="n"/>
+      <c r="P34" s="15" t="n"/>
+      <c r="Q34" s="15" t="n"/>
       <c r="R34" s="5" t="n"/>
       <c r="T34" s="3" t="n"/>
-      <c r="U34" s="13" t="n"/>
-      <c r="V34" s="13" t="n"/>
-      <c r="W34" s="13" t="n"/>
+      <c r="U34" s="15" t="n"/>
+      <c r="V34" s="15" t="n"/>
+      <c r="W34" s="15" t="n"/>
       <c r="X34" s="5" t="n"/>
       <c r="Z34" s="3" t="n"/>
-      <c r="AA34" s="13" t="n"/>
-      <c r="AB34" s="13" t="n"/>
-      <c r="AC34" s="13" t="n"/>
+      <c r="AA34" s="15" t="n"/>
+      <c r="AB34" s="15" t="n"/>
+      <c r="AC34" s="15" t="n"/>
       <c r="AD34" s="5" t="n"/>
     </row>
     <row r="36" ht="27" customHeight="1">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>评分来源：Athieno《OFFICIAL Operator Tier List in Y11S2》｜Y11S2｜覆盖至 Y11S2（2026-06-02）｜发布 2026-06-02｜采集 2026-07-25T00:00:00+08:00</t>
         </is>
       </c>
     </row>
     <row r="37" ht="27" customHeight="1">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>游戏数据：灰机 Wiki｜Y11S2 系统覆盖行动｜Y11S2.2｜抓取 2026-07-26T13:13:13.429371+08:00｜除评分外，其他信息均为该时间点的最新数据</t>
         </is>
       </c>
     </row>
     <row r="38" ht="27" customHeight="1">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>补丁区间：评分覆盖至 2026-06-02；Wiki 数据截至 2026-07-26；Y11S2.1（2026-06-23）→ Y11S2.2（2026-07-14）</t>
         </is>
@@ -12467,1128 +12473,1128 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Y11S2 视频评分后续补丁说明</t>
         </is>
       </c>
     </row>
     <row r="2" ht="31" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>除 Athieno Y11S2 视频评分外，干员、速度、武器、装备、图标与补丁信息均按灰机 Wiki 抓取时间更新。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>补丁范围：2026-06-02 之后至 2026-07-26；以下内容不重新计算视频评分。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Y11S2.1 · 2026-06-23 · 系统覆盖行动</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>灰机 Wiki</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>https://r6s.huijiwiki.com/wiki/Y11S2.1%E6%9B%B4%E6%96%B0%E8%A1%A5%E4%B8%81</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n"/>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="C6" s="28" t="n"/>
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>Ubisoft</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>https://www.ubisoft.com/zh-tw/game/rainbow-six/siege/news-updates/7tAny5W9p4yrHmIiH51noI/y11s21-patch-notes</t>
         </is>
       </c>
-      <c r="F6" s="26" t="n"/>
+      <c r="F6" s="28" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>补丁</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>干员/对象</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>视频评分</t>
         </is>
       </c>
-      <c r="F7" s="27" t="inlineStr">
+      <c r="F7" s="29" t="inlineStr">
         <is>
           <t>更新内容</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>削弱</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D8" s="29" t="inlineStr">
+      <c r="D8" s="31" t="inlineStr">
         <is>
           <t>Dokkaebi</t>
         </is>
       </c>
-      <c r="E8" s="29" t="inlineStr">
+      <c r="E8" s="31" t="inlineStr">
         <is>
           <t>S / 100</t>
         </is>
       </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="F8" s="32" t="inlineStr">
         <is>
           <t>「剿截代码」技能时间结束后增加 7 秒的使用冷却。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D9" s="29" t="inlineStr">
+      <c r="D9" s="31" t="inlineStr">
         <is>
           <t>Sens</t>
         </is>
       </c>
-      <c r="E9" s="29" t="inlineStr">
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t>A / 85</t>
         </is>
       </c>
-      <c r="F9" s="30" t="inlineStr">
+      <c r="F9" s="32" t="inlineStr">
         <is>
           <t>「R.O.U.投影系统」电池续航时间提升至 15 秒（原为13秒）。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D10" s="29" t="inlineStr">
+      <c r="D10" s="31" t="inlineStr">
         <is>
           <t>IQ</t>
         </is>
       </c>
-      <c r="E10" s="29" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t>B / 70</t>
         </is>
       </c>
-      <c r="F10" s="30" t="inlineStr">
+      <c r="F10" s="32" t="inlineStr">
         <is>
           <t>「电子设备侦测器」侦测范围提升至 22 米（原为20米）。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C11" s="29" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D11" s="29" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>Ash</t>
         </is>
       </c>
-      <c r="E11" s="29" t="inlineStr">
+      <c r="E11" s="31" t="inlineStr">
         <is>
           <t>B / 70</t>
         </is>
       </c>
-      <c r="F11" s="30" t="inlineStr">
+      <c r="F11" s="32" t="inlineStr">
         <is>
           <t>「爆破弹」爆炸伤害范围提升至 2.2 米（原为 2 米）。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D12" s="29" t="inlineStr">
+      <c r="D12" s="31" t="inlineStr">
         <is>
           <t>Finka</t>
         </is>
       </c>
-      <c r="E12" s="29" t="inlineStr">
+      <c r="E12" s="31" t="inlineStr">
         <is>
           <t>C / 55</t>
         </is>
       </c>
-      <c r="F12" s="30" t="inlineStr">
+      <c r="F12" s="32" t="inlineStr">
         <is>
           <t>「肾上腺素激发」技能冷却时间降低至 18 秒（原为20秒）。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D13" s="29" t="inlineStr">
+      <c r="D13" s="31" t="inlineStr">
         <is>
           <t>Thatcher</t>
         </is>
       </c>
-      <c r="E13" s="29" t="inlineStr">
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t>A / 85</t>
         </is>
       </c>
-      <c r="F13" s="30" t="inlineStr">
+      <c r="F13" s="32" t="inlineStr">
         <is>
           <t>「E.G.S.干扰器」效果半径提升至 1.85 米（原为1.75米）。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>削弱</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C14" s="29" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D14" s="29" t="inlineStr">
+      <c r="D14" s="31" t="inlineStr">
         <is>
           <t>Thorn</t>
         </is>
       </c>
-      <c r="E14" s="29" t="inlineStr">
+      <c r="E14" s="31" t="inlineStr">
         <is>
           <t>S / 100</t>
         </is>
       </c>
-      <c r="F14" s="30" t="inlineStr">
+      <c r="F14" s="32" t="inlineStr">
         <is>
           <t>「剃刀花榴弹」命中后施加的跛行效果缩短至 10 秒（原为15秒）。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B15" s="29" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C15" s="29" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D15" s="29" t="inlineStr">
+      <c r="D15" s="31" t="inlineStr">
         <is>
           <t>Zero</t>
         </is>
       </c>
-      <c r="E15" s="29" t="inlineStr">
+      <c r="E15" s="31" t="inlineStr">
         <is>
           <t>C / 55</t>
         </is>
       </c>
-      <c r="F15" s="30" t="inlineStr">
+      <c r="F15" s="32" t="inlineStr">
         <is>
           <t>SC3000K降低水平后坐力 。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C16" s="29" t="inlineStr">
+      <c r="C16" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D16" s="29" t="inlineStr">
+      <c r="D16" s="31" t="inlineStr">
         <is>
           <t>Sentry</t>
         </is>
       </c>
-      <c r="E16" s="29" t="inlineStr">
+      <c r="E16" s="31" t="inlineStr">
         <is>
           <t>B / 70</t>
         </is>
       </c>
-      <c r="F16" s="30" t="inlineStr">
+      <c r="F16" s="32" t="inlineStr">
         <is>
           <t>防弹摄像头电磁脉冲波的爆炸范围提升至 0.75 米（原为 0.55 米）。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="31" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B17" s="29" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C17" s="29" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D17" s="29" t="inlineStr">
+      <c r="D17" s="31" t="inlineStr">
         <is>
           <t>Mute</t>
         </is>
       </c>
-      <c r="E17" s="29" t="inlineStr">
+      <c r="E17" s="31" t="inlineStr">
         <is>
           <t>S / 100</t>
         </is>
       </c>
-      <c r="F17" s="30" t="inlineStr">
+      <c r="F17" s="32" t="inlineStr">
         <is>
           <t>防弹摄像头电磁脉冲波的爆炸范围提升至 0.75 米（原为 0.55 米）。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="31" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B18" s="29" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C18" s="29" t="inlineStr">
+      <c r="C18" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D18" s="29" t="inlineStr">
+      <c r="D18" s="31" t="inlineStr">
         <is>
           <t>Castle</t>
         </is>
       </c>
-      <c r="E18" s="29" t="inlineStr">
+      <c r="E18" s="31" t="inlineStr">
         <is>
           <t>A / 85</t>
         </is>
       </c>
-      <c r="F18" s="30" t="inlineStr">
+      <c r="F18" s="32" t="inlineStr">
         <is>
           <t>防弹摄像头电磁脉冲波的爆炸范围提升至 0.75 米（原为 0.55 米）。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B19" s="29" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C19" s="29" t="inlineStr">
+      <c r="C19" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D19" s="29" t="inlineStr">
+      <c r="D19" s="31" t="inlineStr">
         <is>
           <t>Doc</t>
         </is>
       </c>
-      <c r="E19" s="29" t="inlineStr">
+      <c r="E19" s="31" t="inlineStr">
         <is>
           <t>F / 20</t>
         </is>
       </c>
-      <c r="F19" s="30" t="inlineStr">
+      <c r="F19" s="32" t="inlineStr">
         <is>
           <t>防弹摄像头电磁脉冲波的爆炸范围提升至 0.75 米（原为 0.55 米）。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="31" t="inlineStr">
+      <c r="A20" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B20" s="29" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C20" s="29" t="inlineStr">
+      <c r="C20" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D20" s="29" t="inlineStr">
+      <c r="D20" s="31" t="inlineStr">
         <is>
           <t>Kapkan</t>
         </is>
       </c>
-      <c r="E20" s="29" t="inlineStr">
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>C / 55</t>
         </is>
       </c>
-      <c r="F20" s="30" t="inlineStr">
+      <c r="F20" s="32" t="inlineStr">
         <is>
           <t>防弹摄像头电磁脉冲波的爆炸范围提升至 0.75 米（原为 0.55 米）。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="31" t="inlineStr">
+      <c r="A21" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C21" s="29" t="inlineStr">
+      <c r="C21" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D21" s="29" t="inlineStr">
+      <c r="D21" s="31" t="inlineStr">
         <is>
           <t>Jäger</t>
         </is>
       </c>
-      <c r="E21" s="29" t="inlineStr">
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>B / 70</t>
         </is>
       </c>
-      <c r="F21" s="30" t="inlineStr">
+      <c r="F21" s="32" t="inlineStr">
         <is>
           <t>防弹摄像头电磁脉冲波的爆炸范围提升至 0.75 米（原为 0.55 米）。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B22" s="29" t="inlineStr">
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C22" s="29" t="inlineStr">
+      <c r="C22" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D22" s="29" t="inlineStr">
+      <c r="D22" s="31" t="inlineStr">
         <is>
           <t>Frost</t>
         </is>
       </c>
-      <c r="E22" s="29" t="inlineStr">
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>D / 40</t>
         </is>
       </c>
-      <c r="F22" s="30" t="inlineStr">
+      <c r="F22" s="32" t="inlineStr">
         <is>
           <t>防弹摄像头电磁脉冲波的爆炸范围提升至 0.75 米（原为 0.55 米）。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B23" s="29" t="inlineStr">
+      <c r="B23" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C23" s="29" t="inlineStr">
+      <c r="C23" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D23" s="29" t="inlineStr">
+      <c r="D23" s="31" t="inlineStr">
         <is>
           <t>Lesion</t>
         </is>
       </c>
-      <c r="E23" s="29" t="inlineStr">
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>B / 70</t>
         </is>
       </c>
-      <c r="F23" s="30" t="inlineStr">
+      <c r="F23" s="32" t="inlineStr">
         <is>
           <t>防弹摄像头电磁脉冲波的爆炸范围提升至 0.75 米（原为 0.55 米）。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="31" t="inlineStr">
+      <c r="A24" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C24" s="29" t="inlineStr">
+      <c r="C24" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D24" s="29" t="inlineStr">
+      <c r="D24" s="31" t="inlineStr">
         <is>
           <t>Vigil</t>
         </is>
       </c>
-      <c r="E24" s="29" t="inlineStr">
+      <c r="E24" s="31" t="inlineStr">
         <is>
           <t>A / 85</t>
         </is>
       </c>
-      <c r="F24" s="30" t="inlineStr">
+      <c r="F24" s="32" t="inlineStr">
         <is>
           <t>防弹摄像头电磁脉冲波的爆炸范围提升至 0.75 米（原为 0.55 米）。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="A25" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C25" s="29" t="inlineStr">
+      <c r="C25" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D25" s="29" t="inlineStr">
+      <c r="D25" s="31" t="inlineStr">
         <is>
           <t>Goyo</t>
         </is>
       </c>
-      <c r="E25" s="29" t="inlineStr">
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>A / 85</t>
         </is>
       </c>
-      <c r="F25" s="30" t="inlineStr">
+      <c r="F25" s="32" t="inlineStr">
         <is>
           <t>防弹摄像头电磁脉冲波的爆炸范围提升至 0.75 米（原为 0.55 米）。</t>
         </is>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="31" t="inlineStr">
+      <c r="A26" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B26" s="29" t="inlineStr">
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C26" s="29" t="inlineStr">
+      <c r="C26" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D26" s="29" t="inlineStr">
+      <c r="D26" s="31" t="inlineStr">
         <is>
           <t>Melusi</t>
         </is>
       </c>
-      <c r="E26" s="29" t="inlineStr">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>B / 70</t>
         </is>
       </c>
-      <c r="F26" s="30" t="inlineStr">
+      <c r="F26" s="32" t="inlineStr">
         <is>
           <t>防弹摄像头电磁脉冲波的爆炸范围提升至 0.75 米（原为 0.55 米）。</t>
         </is>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="31" t="inlineStr">
+      <c r="A27" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B27" s="29" t="inlineStr">
+      <c r="B27" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C27" s="29" t="inlineStr">
+      <c r="C27" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D27" s="29" t="inlineStr">
+      <c r="D27" s="31" t="inlineStr">
         <is>
           <t>Aruni</t>
         </is>
       </c>
-      <c r="E27" s="29" t="inlineStr">
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>S / 100</t>
         </is>
       </c>
-      <c r="F27" s="30" t="inlineStr">
+      <c r="F27" s="32" t="inlineStr">
         <is>
           <t>防弹摄像头电磁脉冲波的爆炸范围提升至 0.75 米（原为 0.55 米）。</t>
         </is>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="31" t="inlineStr">
+      <c r="A28" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B28" s="29" t="inlineStr">
+      <c r="B28" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C28" s="29" t="inlineStr">
+      <c r="C28" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D28" s="29" t="inlineStr">
+      <c r="D28" s="31" t="inlineStr">
         <is>
           <t>Thunderbird</t>
         </is>
       </c>
-      <c r="E28" s="29" t="inlineStr">
+      <c r="E28" s="31" t="inlineStr">
         <is>
           <t>F / 20</t>
         </is>
       </c>
-      <c r="F28" s="30" t="inlineStr">
+      <c r="F28" s="32" t="inlineStr">
         <is>
           <t>防弹摄像头电磁脉冲波的爆炸范围提升至 0.75 米（原为 0.55 米）。</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="31" t="inlineStr">
+      <c r="A29" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B29" s="31" t="inlineStr">
         <is>
           <t>Y11S2.1</t>
         </is>
       </c>
-      <c r="C29" s="29" t="inlineStr">
+      <c r="C29" s="31" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="D29" s="29" t="inlineStr">
+      <c r="D29" s="31" t="inlineStr">
         <is>
           <t>Fenrir</t>
         </is>
       </c>
-      <c r="E29" s="29" t="inlineStr">
+      <c r="E29" s="31" t="inlineStr">
         <is>
           <t>B / 70</t>
         </is>
       </c>
-      <c r="F29" s="30" t="inlineStr">
+      <c r="F29" s="32" t="inlineStr">
         <is>
           <t>防弹摄像头电磁脉冲波的爆炸范围提升至 0.75 米（原为 0.55 米）。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t>Y11S2.2 · 2026-07-14 · 系统覆盖行动</t>
         </is>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t>灰机 Wiki</t>
         </is>
       </c>
-      <c r="B32" s="25" t="inlineStr">
+      <c r="B32" s="27" t="inlineStr">
         <is>
           <t>https://r6s.huijiwiki.com/wiki/Y11S2.2%E6%9B%B4%E6%96%B0%E8%A1%A5%E4%B8%81</t>
         </is>
       </c>
-      <c r="C32" s="26" t="n"/>
-      <c r="D32" s="24" t="inlineStr">
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="26" t="inlineStr">
         <is>
           <t>Ubisoft</t>
         </is>
       </c>
-      <c r="E32" s="25" t="inlineStr">
+      <c r="E32" s="27" t="inlineStr">
         <is>
           <t>https://www.ubisoft.com/zh-tw/game/rainbow-six/siege/news-updates/3IoMKS8f3AHlOwBQXfiytt/y11s22-midseason-patch-notes</t>
         </is>
       </c>
-      <c r="F32" s="26" t="n"/>
+      <c r="F32" s="28" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="27" t="inlineStr">
+      <c r="A33" s="29" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="B33" s="27" t="inlineStr">
+      <c r="B33" s="29" t="inlineStr">
         <is>
           <t>补丁</t>
         </is>
       </c>
-      <c r="C33" s="27" t="inlineStr">
+      <c r="C33" s="29" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="D33" s="27" t="inlineStr">
+      <c r="D33" s="29" t="inlineStr">
         <is>
           <t>干员/对象</t>
         </is>
       </c>
-      <c r="E33" s="27" t="inlineStr">
+      <c r="E33" s="29" t="inlineStr">
         <is>
           <t>视频评分</t>
         </is>
       </c>
-      <c r="F33" s="27" t="inlineStr">
+      <c r="F33" s="29" t="inlineStr">
         <is>
           <t>更新内容</t>
         </is>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="32" t="inlineStr">
+      <c r="A34" s="34" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
       </c>
-      <c r="B34" s="29" t="inlineStr">
+      <c r="B34" s="31" t="inlineStr">
         <is>
           <t>Y11S2.2</t>
         </is>
       </c>
-      <c r="C34" s="29" t="inlineStr">
+      <c r="C34" s="31" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D34" s="29" t="inlineStr">
+      <c r="D34" s="31" t="inlineStr">
         <is>
           <t>Dokkaebi</t>
         </is>
       </c>
-      <c r="E34" s="29" t="inlineStr">
+      <c r="E34" s="31" t="inlineStr">
         <is>
           <t>S / 100</t>
         </is>
       </c>
-      <c r="F34" s="30" t="inlineStr">
+      <c r="F34" s="32" t="inlineStr">
         <is>
           <t>「剿截代码」现对目标单独计算冷却时间（原为全局固定冷却）。；冷却时间延长至 14 秒（原为 7 秒）。</t>
         </is>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="31" t="inlineStr">
+      <c r="A35" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B35" s="29" t="inlineStr">
+      <c r="B35" s="31" t="inlineStr">
         <is>
           <t>Y11S2.2</t>
         </is>
       </c>
-      <c r="C35" s="29" t="inlineStr">
+      <c r="C35" s="31" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D35" s="29" t="inlineStr">
+      <c r="D35" s="31" t="inlineStr">
         <is>
           <t>Wamai</t>
         </is>
       </c>
-      <c r="E35" s="29" t="inlineStr">
+      <c r="E35" s="31" t="inlineStr">
         <is>
           <t>A / 85</t>
         </is>
       </c>
-      <c r="F35" s="30" t="inlineStr">
+      <c r="F35" s="32" t="inlineStr">
         <is>
           <t>「磁力销毁系统」；充能刷新间隔缩短至 20 秒（原为 40 秒）。；最大总充能数提高至 7 个（原为 6 个）。；启动时间缩短至 0.5 秒（原为 1.5 秒）。；新增机动护盾。；冲击手榴弹被替换为遥控炸药。</t>
         </is>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="32" t="inlineStr">
+      <c r="A36" s="34" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
       </c>
-      <c r="B36" s="29" t="inlineStr">
+      <c r="B36" s="31" t="inlineStr">
         <is>
           <t>Y11S2.2</t>
         </is>
       </c>
-      <c r="C36" s="29" t="inlineStr">
+      <c r="C36" s="31" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D36" s="29" t="inlineStr">
+      <c r="D36" s="31" t="inlineStr">
         <is>
           <t>Jäger</t>
         </is>
       </c>
-      <c r="E36" s="29" t="inlineStr">
+      <c r="E36" s="31" t="inlineStr">
         <is>
           <t>B / 70</t>
         </is>
       </c>
-      <c r="F36" s="30" t="inlineStr">
+      <c r="F36" s="32" t="inlineStr">
         <is>
           <t>调整为3速度与1生命值（原为2速度与2生命值）。；416ccarbine降低水平和垂直后坐力。</t>
         </is>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="31" t="inlineStr">
+      <c r="A37" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B37" s="29" t="inlineStr">
+      <c r="B37" s="31" t="inlineStr">
         <is>
           <t>Y11S2.2</t>
         </is>
       </c>
-      <c r="C37" s="29" t="inlineStr">
+      <c r="C37" s="31" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D37" s="29" t="inlineStr">
+      <c r="D37" s="31" t="inlineStr">
         <is>
           <t>Zofia</t>
         </is>
       </c>
-      <c r="E37" s="29" t="inlineStr">
+      <c r="E37" s="31" t="inlineStr">
         <is>
           <t>A / 85</t>
         </is>
       </c>
-      <c r="F37" s="30" t="inlineStr">
+      <c r="F37" s="32" t="inlineStr">
         <is>
           <t>「KS79“生命线”双管发射器」；震撼弹弹药数量增加至 3 发（原为 2 发）。；冲击弹弹药数量增加至 3 发（原为 2 发）。</t>
         </is>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="31" t="inlineStr">
+      <c r="A38" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B38" s="29" t="inlineStr">
+      <c r="B38" s="31" t="inlineStr">
         <is>
           <t>Y11S2.2</t>
         </is>
       </c>
-      <c r="C38" s="29" t="inlineStr">
+      <c r="C38" s="31" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D38" s="29" t="inlineStr">
+      <c r="D38" s="31" t="inlineStr">
         <is>
           <t>Rauora</t>
         </is>
       </c>
-      <c r="E38" s="29" t="inlineStr">
+      <c r="E38" s="31" t="inlineStr">
         <is>
           <t>B / 70</t>
         </is>
       </c>
-      <c r="F38" s="30" t="inlineStr">
+      <c r="F38" s="32" t="inlineStr">
         <is>
           <t>「D.O.M.装甲板」每次射击之间的冷却时间缩短至 1 秒（原为 3 秒）。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="31" t="inlineStr">
+      <c r="A39" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B39" s="29" t="inlineStr">
+      <c r="B39" s="31" t="inlineStr">
         <is>
           <t>Y11S2.2</t>
         </is>
       </c>
-      <c r="C39" s="29" t="inlineStr">
+      <c r="C39" s="31" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D39" s="29" t="inlineStr">
+      <c r="D39" s="31" t="inlineStr">
         <is>
           <t>Melusi</t>
         </is>
       </c>
-      <c r="E39" s="29" t="inlineStr">
+      <c r="E39" s="31" t="inlineStr">
         <is>
           <t>B / 70</t>
         </is>
       </c>
-      <c r="F39" s="30" t="inlineStr">
+      <c r="F39" s="32" t="inlineStr">
         <is>
           <t>「幽鸣音波防御装置」的作用范围扩大至 4.3 米（原为 4 米）。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="31" t="inlineStr">
+      <c r="A40" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B40" s="29" t="inlineStr">
+      <c r="B40" s="31" t="inlineStr">
         <is>
           <t>Y11S2.2</t>
         </is>
       </c>
-      <c r="C40" s="29" t="inlineStr">
+      <c r="C40" s="31" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D40" s="29" t="inlineStr">
+      <c r="D40" s="31" t="inlineStr">
         <is>
           <t>Twitch</t>
         </is>
       </c>
-      <c r="E40" s="29" t="inlineStr">
+      <c r="E40" s="31" t="inlineStr">
         <is>
           <t>A / 85</t>
         </is>
       </c>
-      <c r="F40" s="30" t="inlineStr">
+      <c r="F40" s="32" t="inlineStr">
         <is>
           <t>「电击无人机」的激光充能时间缩短至 28 秒（原为 30 秒）。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="31" t="inlineStr">
+      <c r="A41" s="33" t="inlineStr">
         <is>
           <t>增强</t>
         </is>
       </c>
-      <c r="B41" s="29" t="inlineStr">
+      <c r="B41" s="31" t="inlineStr">
         <is>
           <t>Y11S2.2</t>
         </is>
       </c>
-      <c r="C41" s="29" t="inlineStr">
+      <c r="C41" s="31" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="D41" s="29" t="inlineStr">
+      <c r="D41" s="31" t="inlineStr">
         <is>
           <t>Lesion</t>
         </is>
       </c>
-      <c r="E41" s="29" t="inlineStr">
+      <c r="E41" s="31" t="inlineStr">
         <is>
           <t>B / 70</t>
         </is>
       </c>
-      <c r="F41" s="30" t="inlineStr">
+      <c r="F41" s="32" t="inlineStr">
         <is>
           <t>「蛊针陷阱」的补充时间缩短至 25 秒（原为 30 秒）。</t>
         </is>
       </c>
     </row>
     <row r="43" ht="27" customHeight="1">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>评分来源：Athieno《OFFICIAL Operator Tier List in Y11S2》｜Y11S2｜覆盖至 Y11S2（2026-06-02）｜发布 2026-06-02｜采集 2026-07-25T00:00:00+08:00</t>
         </is>
       </c>
     </row>
     <row r="44" ht="27" customHeight="1">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>游戏数据：灰机 Wiki｜Y11S2 系统覆盖行动｜Y11S2.2｜抓取 2026-07-26T13:13:13.429371+08:00｜除评分外，其他信息均为该时间点的最新数据</t>
         </is>
       </c>
     </row>
     <row r="45" ht="27" customHeight="1">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>补丁区间：评分覆盖至 2026-06-02；Wiki 数据截至 2026-07-26；Y11S2.1（2026-06-23）→ Y11S2.2（2026-07-14）</t>
         </is>

--- a/docs/主武器射速榜.xlsx
+++ b/docs/主武器射速榜.xlsx
@@ -10215,7 +10215,7 @@
       <c r="J3" s="5" t="n"/>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -10249,7 +10249,7 @@
       <c r="V3" s="5" t="n"/>
       <c r="W3" s="8" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="7" t="inlineStr">
@@ -10514,7 +10514,7 @@
       <c r="AB7" s="5" t="n"/>
       <c r="AC7" s="9" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AD7" s="7" t="inlineStr">
@@ -10745,7 +10745,7 @@
       <c r="V11" s="5" t="n"/>
       <c r="W11" s="17" t="inlineStr">
         <is>
-          <t>F+</t>
+          <t>F</t>
         </is>
       </c>
       <c r="X11" s="7" t="inlineStr">
@@ -10964,7 +10964,7 @@
       <c r="J15" s="5" t="n"/>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -11212,7 +11212,7 @@
       <c r="J19" s="5" t="n"/>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -11471,7 +11471,7 @@
       <c r="V23" s="5" t="n"/>
       <c r="W23" s="8" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="7" t="inlineStr">
@@ -11702,7 +11702,7 @@
       <c r="P27" s="5" t="n"/>
       <c r="Q27" s="10" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
@@ -11719,7 +11719,7 @@
       <c r="V27" s="5" t="n"/>
       <c r="W27" s="17" t="inlineStr">
         <is>
-          <t>F+</t>
+          <t>F</t>
         </is>
       </c>
       <c r="X27" s="7" t="inlineStr">
@@ -11910,7 +11910,7 @@
       <c r="J31" s="5" t="n"/>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
@@ -11944,7 +11944,7 @@
       <c r="V31" s="5" t="n"/>
       <c r="W31" s="21" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X31" s="7" t="inlineStr">
